--- a/supplementary/Supplementary_Dataset_S2_carbon_model.xlsx
+++ b/supplementary/Supplementary_Dataset_S2_carbon_model.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>on the Alfonso et al. (2025) plate model.</t>
+          <t>on the Alfonso et al. (2024) plate model.</t>
         </is>
       </c>
     </row>
@@ -498,14 +498,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Plate influx by reservoir — carbon carried into the plate / sequestered, separated by reservoir,</t>
+          <t xml:space="preserve">  • Plate influx by reservoir — carbon carried down on the subducting plate, separated by reservoir,</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    plus the gross (total) plate influx.</t>
+          <t xml:space="preserve">    plus their total.</t>
         </is>
       </c>
     </row>
@@ -578,53 +578,74 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Serpentinite = total (bending-related + mid-ocean-ridge) serpentinite carbon.</t>
+          <t xml:space="preserve">  • Plate influx covers pelagic carbonate sediment and altered oceanic crust, and the total is</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    their sum. Serpentinite carbon is mantle-derived and returns to the mantle rather than</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Sources (files in the CCD_workflow_clean repository, steps/step10_carbon_cycle_degassing/</t>
+          <t xml:space="preserve">    representing a sink of surface carbon, so it is excluded, as is organic carbon; neither</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">    enters the attribution behind Figure 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Sources (files in the CCD_workflow_clean repository, steps/step10_carbon_cycle_degassing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>Alfonso_etal_2024_DM26/Outputs):</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Atmospheric outflux: Notebook05/csv/05_atmospheric_influx_all_sources.csv</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Plate influx: Notebook02/csv/02_plate_influx.csv</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Net flux: Notebook05/csv/05_net_carbon_outflux.csv</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>See the Provenance sheet for the exact files used and when they were last written.</t>
         </is>
@@ -10916,7 +10937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P173"/>
+  <dimension ref="A1:J173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10929,12 +10950,6 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10959,25 +10974,11 @@
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Serpentinite (total)</t>
+          <t>Total plate influx</t>
         </is>
       </c>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Organic sediments</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Gross plate influx</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="n"/>
-      <c r="P1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n"/>
@@ -11026,36 +11027,6 @@
           <t>max</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -11080,31 +11051,13 @@
         <v>27.47703822213518</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>10.52628083838634</v>
+        <v>154.4350580714534</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10.71688289423511</v>
+        <v>158.2073442955981</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>11.42050044887275</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>5.178613046458163</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>11.35953829545656</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>172.1090659539454</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>188.0598887421909</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>208.631367988189</v>
+        <v>162.8621265277024</v>
       </c>
     </row>
     <row r="4">
@@ -11130,31 +11083,13 @@
         <v>27.47703822213518</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>10.63678363685799</v>
+        <v>157.8712451663239</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>10.85841715564967</v>
+        <v>161.6435313904686</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>11.67813661029904</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>5.30324036115829</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>11.63291434060523</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>175.5452530488159</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>191.6207031517615</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>213.3364845048118</v>
+        <v>166.2983136225729</v>
       </c>
     </row>
     <row r="5">
@@ -11180,31 +11115,13 @@
         <v>28.50861851011271</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>10.53577683812358</v>
+        <v>158.6227392137676</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10.73304225712519</v>
+        <v>162.5188713553684</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>11.46848634734051</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>5.352709256876566</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>11.74142675701961</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>176.1881378422582</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>192.7678659536444</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>214.4051036788713</v>
+        <v>167.3298939105505</v>
       </c>
     </row>
     <row r="6">
@@ -11230,31 +11147,13 @@
         <v>28.64008777554652</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.66547270964584</v>
+        <v>221.5744479842251</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.96243179972614</v>
+        <v>225.2860931223189</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.74630841755255</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>5.275601555607267</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>11.5722872832676</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>239.2695424842378</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>255.6873695619265</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>277.2715726284956</v>
+        <v>230.0876802637147</v>
       </c>
     </row>
     <row r="7">
@@ -11280,31 +11179,13 @@
         <v>28.95239951961132</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.64773115821434</v>
+        <v>221.7543105729778</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.9380268851418</v>
+        <v>225.6663706927328</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.69007696739053</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>5.216623971357163</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>11.44291709846092</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>239.6600183754192</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>255.7994427952415</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>277.3770296110785</v>
+        <v>230.4971875383753</v>
       </c>
     </row>
     <row r="8">
@@ -11330,31 +11211,13 @@
         <v>29.06510389664324</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10.78481181142345</v>
+        <v>221.2000798267587</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.05156364299943</v>
+        <v>225.0796547524479</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>11.74673850722989</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>5.216623971357163</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>11.44291709846092</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>239.3182696752503</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>255.3366497704186</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>276.2021053291268</v>
+        <v>229.8616608168662</v>
       </c>
     </row>
     <row r="9">
@@ -11380,31 +11243,13 @@
         <v>29.24161338328425</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>11.113034458335</v>
+        <v>219.4101860642507</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11.32382090040977</v>
+        <v>223.3438612207081</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11.98821642532715</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>5.147415053013168</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>11.29110398725474</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>237.9359839062364</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>253.9451363686019</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>274.9269594511684</v>
+        <v>228.1863995238551</v>
       </c>
     </row>
     <row r="10">
@@ -11430,31 +11275,13 @@
         <v>29.32812895786688</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11.09813887374548</v>
+        <v>219.2005755953165</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.39710234684522</v>
+        <v>223.0856275535023</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>12.07565096692035</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>5.135017363686457</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>11.26390905582841</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>237.831628575003</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>253.6810198383492</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>274.6300351615694</v>
+        <v>227.8019931775971</v>
       </c>
     </row>
     <row r="11">
@@ -11480,31 +11307,13 @@
         <v>29.71956851143239</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>11.00590463298093</v>
+        <v>221.4459618859909</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11.25421601417231</v>
+        <v>225.4898214922918</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>11.94007552851755</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>5.258529187245306</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>11.53483821718325</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>240.0950163092044</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>256.1446551156979</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>277.4360776568967</v>
+        <v>230.3740300388218</v>
       </c>
     </row>
     <row r="12">
@@ -11530,31 +11339,13 @@
         <v>29.90584858444288</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>10.79513827723659</v>
+        <v>221.6195600698785</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.08781610032333</v>
+        <v>225.6219859170689</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>11.76979824805186</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>5.684284822903038</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>12.46875380507765</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>240.1070292410005</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>256.6185532290418</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>278.6542933959016</v>
+        <v>230.4569428060154</v>
       </c>
     </row>
     <row r="13">
@@ -11580,31 +11371,13 @@
         <v>30.34107963397419</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10.62963087410898</v>
+        <v>223.1943942343223</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10.92230869719572</v>
+        <v>227.2009536835384</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>11.60429084492426</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>5.982297389974037</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>13.12245879091091</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>241.5650844402466</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>258.6433513611854</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>281.2073996672224</v>
+        <v>232.2523141314112</v>
       </c>
     </row>
     <row r="14">
@@ -11630,31 +11403,13 @@
         <v>30.34107963397419</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>10.52499602981517</v>
+        <v>222.1268438653163</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10.79956456027542</v>
+        <v>226.1334033145324</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>11.49226632171989</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>5.767544089734954</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>12.65138703554776</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>240.3229264908764</v>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v>257.2689149433706</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>280.9929825838977</v>
+        <v>231.1847637624052</v>
       </c>
     </row>
     <row r="15">
@@ -11680,31 +11435,13 @@
         <v>30.34107963397419</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>10.4674863905321</v>
+        <v>219.3854858821695</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10.78036823843161</v>
+        <v>223.3920453313856</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>11.6158046259759</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>5.74327745504666</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>12.59815699816698</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>237.6105990389604</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>254.4574004377649</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>278.2654305916643</v>
+        <v>228.4434057792584</v>
       </c>
     </row>
     <row r="16">
@@ -11730,31 +11467,13 @@
         <v>30.4394232570271</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>10.4674863905321</v>
+        <v>217.6972746593116</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10.78036823843161</v>
+        <v>221.7129693883801</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>11.6158046259759</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>5.527121548674041</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>12.1240085583817</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>236.165466893447</v>
-      </c>
-      <c r="O16" s="4" t="n">
-        <v>252.6313458549288</v>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v>276.1260282032113</v>
+        <v>226.7781518305907</v>
       </c>
     </row>
     <row r="17">
@@ -11780,31 +11499,13 @@
         <v>30.78115487367424</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>10.35980723746755</v>
+        <v>218.7783614429636</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>10.67268908536706</v>
+        <v>222.9186949274299</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>11.50812547291136</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>5.516311558203426</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>12.10029632122035</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>237.5297580223997</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>254.2444093982643</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>277.7816082278089</v>
+        <v>227.9160824331086</v>
       </c>
     </row>
     <row r="18">
@@ -11830,31 +11531,13 @@
         <v>31.52941796468037</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>10.37164638523081</v>
+        <v>217.4726104809807</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>10.68160061888092</v>
+        <v>221.6413741118882</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>11.65794199736083</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>5.514085719519012</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>12.09541383636422</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>236.255110080472</v>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v>252.9839559793344</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>277.0677663657361</v>
+        <v>226.7914157914168</v>
       </c>
     </row>
     <row r="19">
@@ -11880,31 +11563,13 @@
         <v>32.07561369146125</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>10.47932553829536</v>
+        <v>217.5718809281684</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.78927977194547</v>
+        <v>221.8416203982706</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11.76562115042537</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>5.68306298908832</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>12.46607365348418</v>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>236.5336613419171</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>253.5243031599672</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>277.5835852031418</v>
+        <v>227.1163795103477</v>
       </c>
     </row>
     <row r="20">
@@ -11930,31 +11595,13 @@
         <v>31.41559735404222</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>10.16960012601838</v>
+        <v>215.9994286773863</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10.3826472541064</v>
+        <v>220.1745452605388</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>11.15293009538895</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>5.506040900783808</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>12.07776713720313</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>234.6733029727067</v>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>251.364298475926</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>274.5576716833544</v>
+        <v>225.3076654616762</v>
       </c>
     </row>
     <row r="21">
@@ -11980,31 +11627,13 @@
         <v>31.71082792545488</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>10.16922814232674</v>
+        <v>216.050041763477</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10.36706631095855</v>
+        <v>220.2935594268564</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11.1266926871853</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>5.350701414343775</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>11.73702245727018</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>234.671962037924</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>251.3334366346384</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>274.0298844321956</v>
+        <v>225.5125674066441</v>
       </c>
     </row>
     <row r="22">
@@ -12030,31 +11659,13 @@
         <v>31.71082792545488</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>10.22748726765759</v>
+        <v>215.8324727572803</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>10.42335612489241</v>
+        <v>220.0759904206597</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>11.24523393968944</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>5.264783139643511</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>11.54855656437935</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>234.6476710621359</v>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>251.2168666568779</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>273.7423912609839</v>
+        <v>225.2949984004474</v>
       </c>
     </row>
     <row r="23">
@@ -12080,31 +11691,13 @@
         <v>31.71082792545488</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>10.34363067910235</v>
+        <v>216.238449148011</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>10.54751123321283</v>
+        <v>220.4819668113904</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>11.42436593594451</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>5.260450901631962</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>11.5390535906766</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>235.2319961025632</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>251.78443456346</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>273.9814927190464</v>
+        <v>225.7009747911781</v>
       </c>
     </row>
     <row r="24">
@@ -12130,31 +11723,13 @@
         <v>31.79573143904706</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>9.694610350166055</v>
+        <v>219.341411865302</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9.913333404858641</v>
+        <v>223.6045905510088</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>11.3489422337801</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>5.314529253430119</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>11.65767707204022</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>237.7096233483147</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>254.3299081948888</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>277.2984861713543</v>
+        <v>228.8456575832894</v>
       </c>
     </row>
     <row r="25">
@@ -12180,31 +11755,13 @@
         <v>31.81185295503698</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>9.654281954814779</v>
+        <v>222.184241945133</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9.858649981464584</v>
+        <v>226.4413605235077</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>11.0552030718422</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>5.314529253430119</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>11.65767707204022</v>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>240.6161799515968</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>257.2204299425339</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>279.53730386604</v>
+        <v>231.6779307195296</v>
       </c>
     </row>
     <row r="26">
@@ -12230,31 +11787,13 @@
         <v>33.03464415492809</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>9.654281954814779</v>
+        <v>226.0416663051444</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.858649981464584</v>
+        <v>230.4567147266181</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>11.2669027144135</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>5.285904410488648</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>11.59488709397508</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>244.80341226433</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>261.8237768573925</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>285.0698164061585</v>
+        <v>235.8855236248846</v>
       </c>
     </row>
     <row r="27">
@@ -12280,31 +11819,13 @@
         <v>33.45016474283771</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>9.654281954814779</v>
+        <v>228.2086586140358</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.858649981464584</v>
+        <v>232.6637762295406</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>11.2669027144135</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>5.285904410488648</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>11.59488709397508</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>247.1403465410891</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>264.5639413440106</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>288.1845926565171</v>
+        <v>238.1440070263861</v>
       </c>
     </row>
     <row r="28">
@@ -12330,31 +11851,13 @@
         <v>33.45016474283771</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>9.654281954814779</v>
+        <v>231.9196582609996</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.858649981464584</v>
+        <v>236.3569510534949</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>11.2669027144135</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>5.303352658115877</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>11.63316066941543</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>250.8808836913758</v>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>268.3300855360971</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>291.9160410559117</v>
+        <v>241.8371818503404</v>
       </c>
     </row>
     <row r="29">
@@ -12380,31 +11883,13 @@
         <v>33.45016474283771</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.635620359006932</v>
+        <v>231.9196582609996</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.845692685902062</v>
+        <v>236.3569510534949</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>11.20243990895951</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>5.303352658115877</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>11.63316066941543</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>250.9675280720564</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>268.3941456531942</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>292.2215590684021</v>
+        <v>241.8371818503404</v>
       </c>
     </row>
     <row r="30">
@@ -12430,31 +11915,13 @@
         <v>33.45016474283771</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.582620420412098</v>
+        <v>233.4678648263825</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.792649239996242</v>
+        <v>237.9051576188778</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.08792741414616</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>5.420439525762133</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>11.88999637909109</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>252.4840752768457</v>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v>269.9253260516243</v>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v>294.1745655898229</v>
+        <v>243.3853884157233</v>
       </c>
     </row>
     <row r="31">
@@ -12480,31 +11947,13 @@
         <v>33.42350574448867</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.860348913421438</v>
+        <v>233.4500400033729</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.02920267711752</v>
+        <v>237.9018250156334</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.39847511089708</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>5.448139820355529</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>11.95075831561859</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>252.776623091945</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>270.5658303892469</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>294.4191751855688</v>
+        <v>243.3587294173743</v>
       </c>
     </row>
     <row r="32">
@@ -12530,31 +11979,13 @@
         <v>33.42350574448867</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.23482456499122</v>
+        <v>233.8779486711704</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.47227004100824</v>
+        <v>238.3297336834309</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.61754308411584</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>5.906027662765452</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>12.95515745380804</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>253.716231212493</v>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v>272.5869243636517</v>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v>298.3283487339773</v>
+        <v>243.7866380851717</v>
       </c>
     </row>
     <row r="33">
@@ -12580,31 +12011,13 @@
         <v>33.59934523756261</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.58262882784606</v>
+        <v>234.0422355346901</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.8932594057221</v>
+        <v>238.4901949376095</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>12.12248429690741</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>5.906027662765452</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>12.95515745380804</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>254.3283927430507</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>273.7215627468179</v>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>300.1684894968104</v>
+        <v>243.9624775782457</v>
       </c>
     </row>
     <row r="34">
@@ -12630,31 +12043,13 @@
         <v>33.59934523756261</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.75199603939682</v>
+        <v>232.5783798004821</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.06845444107539</v>
+        <v>237.0263392034014</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.29767933226071</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>5.270285418045868</v>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>11.56062607829414</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>252.9407198171608</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>271.6889218060903</v>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v>297.0356449032078</v>
+        <v>242.4986218440376</v>
       </c>
     </row>
     <row r="35">
@@ -12680,31 +12075,13 @@
         <v>33.64017260734744</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>10.72669972463759</v>
+        <v>213.6613021899424</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.05769379783362</v>
+        <v>218.1100854090754</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.43330181691766</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>5.475746171761962</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>12.01131418321972</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>233.9609960147976</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>252.7425990833846</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>277.5015092664652</v>
+        <v>223.5700295356013</v>
       </c>
     </row>
     <row r="36">
@@ -12730,31 +12107,13 @@
         <v>33.81601210042138</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>10.80281549696692</v>
+        <v>211.158476230037</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>11.11560976616245</v>
+        <v>215.7492648488666</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>12.48367899784299</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>5.543380437737454</v>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>12.15967321826277</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>231.8469300504365</v>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v>250.0241104303087</v>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>275.0155811480658</v>
+        <v>221.2245872142879</v>
       </c>
     </row>
     <row r="37">
@@ -12780,31 +12139,13 @@
         <v>33.41106026722442</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>10.79382658482575</v>
+        <v>207.0678137229872</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>11.1203863876587</v>
+        <v>211.6075409599974</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>12.45021901079875</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>5.434626548809479</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>11.92111630061442</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>227.6023897717947</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>245.2876816001533</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>270.5773826205949</v>
+        <v>217.1864467507561</v>
       </c>
     </row>
     <row r="38">
@@ -12830,31 +12171,13 @@
         <v>32.82952532158728</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>11.00997704394686</v>
+        <v>193.6243203931643</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>11.35840759328144</v>
+        <v>197.9222455564174</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>12.48771613062714</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>5.428209244618817</v>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>11.90703963335747</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>214.212435177636</v>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>231.7156653634801</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>256.154912021732</v>
+        <v>203.4041109205851</v>
       </c>
     </row>
     <row r="39">
@@ -12880,31 +12203,13 @@
         <v>33.13591715623995</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>10.970863581836</v>
+        <v>186.3357833282776</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>11.28053573098722</v>
+        <v>190.7812027659519</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>12.41801315094367</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>5.466765203971485</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>11.99161399580846</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>206.8858424957049</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>224.1922508053337</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>247.7789989101482</v>
+        <v>196.2914884951262</v>
       </c>
     </row>
     <row r="40">
@@ -12930,31 +12235,13 @@
         <v>33.36945699036428</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>10.5511819730407</v>
+        <v>183.4314904673344</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>10.88199240425831</v>
+        <v>187.8922210510199</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>12.10018959376026</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>5.45649560854278</v>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>11.96908714131965</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>203.5681118838164</v>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v>220.7629492342677</v>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v>244.523792062758</v>
+        <v>193.3930059060352</v>
       </c>
     </row>
     <row r="41">
@@ -12980,31 +12267,13 @@
         <v>34.06390343497221</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>10.46309412839325</v>
+        <v>178.13010729033</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>10.79571951208653</v>
+        <v>182.6963124668284</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>12.00534476650706</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>5.59823319430182</v>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>12.27999539395238</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>198.2828126471992</v>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>214.8753813353416</v>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v>239.339975288864</v>
+        <v>188.3332691470513</v>
       </c>
     </row>
     <row r="42">
@@ -13030,31 +12299,13 @@
         <v>34.38680697466032</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>10.44721199906117</v>
+        <v>173.6944233343974</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10.77983738275445</v>
+        <v>178.3306607751101</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>11.98946263717499</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>5.633930844320541</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>12.35829991657419</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>193.8471286912666</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>210.5454272936419</v>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>234.8143737171906</v>
+        <v>184.0360067258949</v>
       </c>
     </row>
     <row r="43">
@@ -13080,31 +12331,13 @@
         <v>34.41140373888675</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>10.27866195284706</v>
+        <v>167.4766807226931</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10.61128733654034</v>
+        <v>172.0622730435736</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>11.82091259096088</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>5.512949486298296</v>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>12.09292145381571</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>187.4808909650857</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>203.9507577354422</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>227.9319237013425</v>
+        <v>177.7454644354616</v>
       </c>
     </row>
     <row r="44">
@@ -13130,31 +12363,13 @@
         <v>34.40539994896718</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>10.2289934124982</v>
+        <v>163.363006352665</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10.56161879619148</v>
+        <v>167.9565000538376</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>11.77124405061202</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>5.5284793339562</v>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>12.12698692609746</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>183.1877203181336</v>
-      </c>
-      <c r="O44" s="4" t="n">
-        <v>199.7314441847804</v>
-      </c>
-      <c r="P44" s="4" t="n">
-        <v>223.4473188406826</v>
+        <v>173.618699548544</v>
       </c>
     </row>
     <row r="45">
@@ -13180,31 +12395,13 @@
         <v>34.24942692327303</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>10.20908045497392</v>
+        <v>163.2453137171775</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>10.56163131567908</v>
+        <v>167.8219972478038</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>11.71509208033707</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>5.5284793339562</v>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>12.12698692609746</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>183.0463713819571</v>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v>199.5124204885026</v>
-      </c>
-      <c r="P45" s="4" t="n">
-        <v>221.0130073670063</v>
+        <v>173.4627265228499</v>
       </c>
     </row>
     <row r="46">
@@ -13230,31 +12427,13 @@
         <v>34.01772745334442</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>10.17220014612993</v>
+        <v>161.8793127231431</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10.50757885405135</v>
+        <v>166.4294319969526</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>11.51825543040805</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>5.5284793339562</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>12.12698692609746</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>181.5801495977466</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>197.7772467875198</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>219.0963032949655</v>
+        <v>172.0361730058987</v>
       </c>
     </row>
     <row r="47">
@@ -13280,31 +12459,13 @@
         <v>34.01772745334442</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>10.14457588250026</v>
+        <v>158.8490121227319</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>10.41786556085723</v>
+        <v>163.3991313965414</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>11.31652441176181</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>5.475409927193511</v>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v>12.01057661448909</v>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v>178.5142711030077</v>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v>194.5913507493289</v>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v>215.5584004367241</v>
+        <v>169.0058724054875</v>
       </c>
     </row>
     <row r="48">
@@ -13330,31 +12491,13 @@
         <v>34.01772745334442</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>10.23891630795921</v>
+        <v>153.9766692899457</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>10.53454441021293</v>
+        <v>158.5267885637552</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>11.39095014169422</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>5.439712277174789</v>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v>11.93227209186728</v>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v>173.6472313730538</v>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v>189.6439951786111</v>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v>210.1131738342961</v>
+        <v>164.1335295727013</v>
       </c>
     </row>
     <row r="49">
@@ -13380,31 +12523,13 @@
         <v>33.73055545333186</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>10.20076073602888</v>
+        <v>150.2639172974494</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>10.52770570249666</v>
+        <v>154.6834274725154</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>11.4516178312915</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v>6.196288423944813</v>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>13.59185847833059</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>170.0365313753122</v>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v>186.6199748661053</v>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v>208.071965068903</v>
+        <v>160.2735973225395</v>
       </c>
     </row>
     <row r="50">
@@ -13430,31 +12555,13 @@
         <v>33.12234329009603</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>10.73013622181832</v>
+        <v>130.3431146684611</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11.07837250708106</v>
+        <v>134.9521010242998</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>11.7822117506335</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>5.863537422705946</v>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>12.86195305625814</v>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>150.6449710756898</v>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v>166.5989999291394</v>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>188.1364304327298</v>
+        <v>140.5954059658575</v>
       </c>
     </row>
     <row r="51">
@@ -13480,31 +12587,13 @@
         <v>32.69975673562644</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>10.56772256384379</v>
+        <v>120.173012857147</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>10.90984110956398</v>
+        <v>125.3172999121978</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>11.91793686566344</v>
-      </c>
-      <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v>5.201148494737384</v>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v>11.40897089168208</v>
-      </c>
-      <c r="N51" s="4" t="n">
-        <v>140.4273983849769</v>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v>156.834287961455</v>
-      </c>
-      <c r="P51" s="4" t="n">
-        <v>177.5953122204077</v>
+        <v>130.6533268739574</v>
       </c>
     </row>
     <row r="52">
@@ -13530,31 +12619,13 @@
         <v>32.5404785167248</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>11.00970865127531</v>
+        <v>107.82865999458</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11.34998621416603</v>
+        <v>112.0377267575399</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>12.3561726258019</v>
-      </c>
-      <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="n">
-        <v>5.157193346574259</v>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v>11.3125531473242</v>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v>128.6181865958912</v>
-      </c>
-      <c r="O52" s="4" t="n">
-        <v>144.7713662198628</v>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v>166.2666721863045</v>
+        <v>118.0727179582598</v>
       </c>
     </row>
     <row r="53">
@@ -13580,31 +12651,13 @@
         <v>32.33361812283412</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>11.19728129765764</v>
+        <v>108.5153399774919</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>11.51382832889856</v>
+        <v>112.6048789546857</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>12.54755852330014</v>
-      </c>
-      <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v>5.157193346574259</v>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v>11.3125531473242</v>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>129.7814978630789</v>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v>145.450143028223</v>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v>166.6717353024928</v>
+        <v>118.4422427263802</v>
       </c>
     </row>
     <row r="54">
@@ -13630,31 +12683,13 @@
         <v>32.25412964738003</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>11.30942345072514</v>
+        <v>108.2771970388165</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>11.57720626277269</v>
+        <v>112.3667360160103</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>12.47800197215204</v>
-      </c>
-      <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v>5.157193346574259</v>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v>11.3125531473242</v>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>129.7203443812336</v>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v>145.3030435808714</v>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v>166.3238994182622</v>
+        <v>118.1246113122507</v>
       </c>
     </row>
     <row r="55">
@@ -13680,31 +12715,13 @@
         <v>32.33361812283412</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>11.36334830483566</v>
+        <v>103.7282402169061</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>11.70542898867516</v>
+        <v>107.9330877687715</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>12.76960267531943</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v>5.116505987341133</v>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>11.2233034561032</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>125.2312550138586</v>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v>140.9996174934754</v>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>162.1181283554614</v>
+        <v>113.6551429657945</v>
       </c>
     </row>
     <row r="56">
@@ -13730,31 +12747,13 @@
         <v>32.6431766997303</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>11.43270206390597</v>
+        <v>97.75224350030351</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>11.78176142498442</v>
+        <v>102.0680409935849</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>12.89830546472638</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v>5.140953526695198</v>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v>11.27693031662174</v>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>119.3553599541365</v>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v>135.2574418129961</v>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v>156.2890509976846</v>
+        <v>107.5419263225568</v>
       </c>
     </row>
     <row r="57">
@@ -13780,31 +12779,13 @@
         <v>33.27962714655078</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>11.32249165567256</v>
+        <v>97.85975330467457</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>11.66242368850195</v>
+        <v>102.8223739768799</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>12.77789040087663</v>
-      </c>
-      <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="n">
-        <v>4.988213948344873</v>
-      </c>
-      <c r="M57" s="4" t="n">
-        <v>10.94188866088561</v>
-      </c>
-      <c r="N57" s="4" t="n">
-        <v>119.2985909382902</v>
-      </c>
-      <c r="O57" s="4" t="n">
-        <v>135.7304771874776</v>
-      </c>
-      <c r="P57" s="4" t="n">
-        <v>156.2816644958216</v>
+        <v>108.1783767693773</v>
       </c>
     </row>
     <row r="58">
@@ -13830,31 +12811,13 @@
         <v>33.62785727032635</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>11.19506953175696</v>
+        <v>108.4792692684636</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11.53342724732661</v>
+        <v>113.5241827700323</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>12.59975422268392</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v>5.164968604350039</v>
-      </c>
-      <c r="M58" s="4" t="n">
-        <v>11.32960855147745</v>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v>129.5627971173878</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>146.6362443245184</v>
-      </c>
-      <c r="P58" s="4" t="n">
-        <v>167.6511043288975</v>
+        <v>119.1600967118613</v>
       </c>
     </row>
     <row r="59">
@@ -13880,31 +12843,13 @@
         <v>33.33612133261431</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>11.57201893501395</v>
+        <v>108.9216546395994</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>11.9395082520305</v>
+        <v>113.3769821028011</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>12.90822997405876</v>
-      </c>
-      <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v>4.907053131433486</v>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v>10.76385848185404</v>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>129.8463814309826</v>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v>146.0969767782959</v>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v>167.1313971979889</v>
+        <v>118.8683607741493</v>
       </c>
     </row>
     <row r="60">
@@ -13930,31 +12875,13 @@
         <v>31.93049841867522</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>11.60836369190051</v>
+        <v>106.9730869467217</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>12.00605299327371</v>
+        <v>111.1467149702506</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>12.91135750212515</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>4.328793296317381</v>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v>9.495417553212262</v>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>127.5070890346982</v>
-      </c>
-      <c r="O60" s="4" t="n">
-        <v>143.8941733189822</v>
-      </c>
-      <c r="P60" s="4" t="n">
-        <v>164.028251435306</v>
+        <v>116.4976518707538</v>
       </c>
     </row>
     <row r="61">
@@ -13980,31 +12907,13 @@
         <v>35.02952259675721</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>11.69917253536278</v>
+        <v>108.3687458273759</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12.04540940230431</v>
+        <v>113.0943991421456</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>13.01655064211632</v>
-      </c>
-      <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="n">
-        <v>4.386939655180049</v>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>9.622964404911167</v>
-      </c>
-      <c r="N61" s="4" t="n">
-        <v>128.9372205299433</v>
-      </c>
-      <c r="O61" s="4" t="n">
-        <v>145.8888675128161</v>
-      </c>
-      <c r="P61" s="4" t="n">
-        <v>166.5389058793835</v>
+        <v>118.8810367354172</v>
       </c>
     </row>
     <row r="62">
@@ -14030,31 +12939,13 @@
         <v>35.69098080449227</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>11.46669214783807</v>
+        <v>104.8141826761258</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11.87568842328431</v>
+        <v>109.7047137283623</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>12.6701028626516</v>
-      </c>
-      <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v>4.568739826904174</v>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v>10.02175187837041</v>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v>125.2645554204938</v>
-      </c>
-      <c r="O62" s="4" t="n">
-        <v>142.6798288771082</v>
-      </c>
-      <c r="P62" s="4" t="n">
-        <v>163.7023381948454</v>
+        <v>115.722024395407</v>
       </c>
     </row>
     <row r="63">
@@ -14080,31 +12971,13 @@
         <v>36.24501428492478</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>11.01129408335841</v>
+        <v>98.28908317804402</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>11.41736666788199</v>
+        <v>103.2180473557713</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>12.5664984772362</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="4" t="n">
-        <v>4.520839486050975</v>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>9.916680162950522</v>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v>118.2931601685268</v>
-      </c>
-      <c r="O63" s="4" t="n">
-        <v>135.83582153815</v>
-      </c>
-      <c r="P63" s="4" t="n">
-        <v>158.4291800771357</v>
+        <v>109.2873015844595</v>
       </c>
     </row>
     <row r="64">
@@ -14130,31 +13003,13 @@
         <v>36.24501428492478</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>10.85502135451908</v>
+        <v>90.7027653792463</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>11.1814744769166</v>
+        <v>95.6247811454285</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>12.42908709703337</v>
-      </c>
-      <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v>4.561763776871023</v>
-      </c>
-      <c r="M64" s="4" t="n">
-        <v>10.00644957507194</v>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>110.5505696408898</v>
-      </c>
-      <c r="O64" s="4" t="n">
-        <v>128.0764477258035</v>
-      </c>
-      <c r="P64" s="4" t="n">
-        <v>151.378816513775</v>
+        <v>101.6940353741168</v>
       </c>
     </row>
     <row r="65">
@@ -14180,31 +13035,13 @@
         <v>39.86449471115338</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>10.84056404350722</v>
+        <v>92.62885014003854</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>11.16701716590475</v>
+        <v>98.0297703320804</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>12.41462978602152</v>
-      </c>
-      <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v>5.089457121485815</v>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>11.16397046003336</v>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v>113.5140608346864</v>
-      </c>
-      <c r="O65" s="4" t="n">
-        <v>132.3805698759167</v>
-      </c>
-      <c r="P65" s="4" t="n">
-        <v>157.2859137151647</v>
+        <v>104.6899695728808</v>
       </c>
     </row>
     <row r="66">
@@ -14230,31 +13067,13 @@
         <v>41.50050211734678</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>10.78916905564782</v>
+        <v>93.30278245476033</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11.11562217804535</v>
+        <v>98.96305664804973</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>12.36323479816212</v>
-      </c>
-      <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="n">
-        <v>5.082481071452662</v>
-      </c>
-      <c r="M66" s="4" t="n">
-        <v>11.14866815673489</v>
-      </c>
-      <c r="N66" s="4" t="n">
-        <v>114.556426462037</v>
-      </c>
-      <c r="O66" s="4" t="n">
-        <v>133.3842852293979</v>
-      </c>
-      <c r="P66" s="4" t="n">
-        <v>158.5155585162928</v>
+        <v>105.9349166773073</v>
       </c>
     </row>
     <row r="67">
@@ -14280,31 +13099,13 @@
         <v>41.58943084661005</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>11.33527341938815</v>
+        <v>88.17100073530396</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>11.71676540216467</v>
+        <v>93.87738416959333</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>12.72305063999365</v>
-      </c>
-      <c r="K67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v>5.041556780632615</v>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v>11.05889874461348</v>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v>110.2181323760939</v>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v>128.926097163348</v>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v>153.3520396061844</v>
+        <v>100.8680327882349</v>
       </c>
     </row>
     <row r="68">
@@ -14330,31 +13131,13 @@
         <v>41.25875969024973</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>11.36867316831719</v>
+        <v>86.42936307006904</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11.71214450125795</v>
+        <v>92.09565277505479</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>12.80028340951024</v>
-      </c>
-      <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v>5.082481071452662</v>
-      </c>
-      <c r="M68" s="4" t="n">
-        <v>11.14866815673489</v>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v>108.3873926834706</v>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v>127.0538524115653</v>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v>151.8534065063442</v>
+        <v>98.9716493561387</v>
       </c>
     </row>
     <row r="69">
@@ -14380,31 +13163,13 @@
         <v>40.0471463224025</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>11.09352148297256</v>
+        <v>77.62306647637182</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>11.42168152168511</v>
+        <v>83.20678154755629</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>12.50612709923654</v>
-      </c>
-      <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v>5.082481071452662</v>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v>11.14866815673489</v>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v>99.42816491684442</v>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v>117.9791408747117</v>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v>142.7915894238497</v>
+        <v>90.0903370660609</v>
       </c>
     </row>
     <row r="70">
@@ -14430,31 +13195,13 @@
         <v>40.0471463224025</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>10.73952418145433</v>
+        <v>75.92072051878402</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11.07775116312828</v>
+        <v>81.50909956221938</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>12.03104573949481</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v>5.082481071452662</v>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>11.14866815673489</v>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>97.44483451445424</v>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v>115.881600515508</v>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v>141.4214549963605</v>
+        <v>88.3879911084731</v>
       </c>
     </row>
     <row r="71">
@@ -14480,31 +13227,13 @@
         <v>39.9201151633921</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>10.41540074139728</v>
+        <v>75.02693513990417</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>10.72318372261658</v>
+        <v>80.53193994423142</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>11.79692929434902</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v>5.040364063706039</v>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>11.05628246232292</v>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>96.03177998429028</v>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v>114.3969438970258</v>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v>139.1071567074658</v>
+        <v>87.26848040998506</v>
       </c>
     </row>
     <row r="72">
@@ -14530,31 +13259,13 @@
         <v>39.51058937064579</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>10.09706059122046</v>
+        <v>69.2211330984526</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>10.37504168184096</v>
+        <v>74.68758244011623</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>11.39760803393604</v>
-      </c>
-      <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v>5.013788431420059</v>
-      </c>
-      <c r="M72" s="4" t="n">
-        <v>10.9979875269859</v>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v>90.20409943283371</v>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v>107.9565624190051</v>
-      </c>
-      <c r="P72" s="4" t="n">
-        <v>131.8255508396087</v>
+        <v>81.4186396068506</v>
       </c>
     </row>
     <row r="73">
@@ -14580,31 +13291,13 @@
         <v>39.50067776847708</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>10.04627337122996</v>
+        <v>65.30300802394089</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10.32093205157451</v>
+        <v>70.79678324656156</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>11.45700062804532</v>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>4.839922425213222</v>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v>10.61660402949997</v>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v>86.05883961395273</v>
-      </c>
-      <c r="O73" s="4" t="n">
-        <v>103.7658050660868</v>
-      </c>
-      <c r="P73" s="4" t="n">
-        <v>127.5693074915799</v>
+        <v>77.52259278337812</v>
       </c>
     </row>
     <row r="74">
@@ -14630,31 +13323,13 @@
         <v>39.50067776847708</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>10.02826569853833</v>
+        <v>65.14508122297113</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10.30404727049227</v>
+        <v>70.63885644559181</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>11.44727756791397</v>
-      </c>
-      <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="4" t="n">
-        <v>4.407908768095036</v>
-      </c>
-      <c r="M74" s="4" t="n">
-        <v>9.668961168724614</v>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>85.86824875065534</v>
-      </c>
-      <c r="O74" s="4" t="n">
-        <v>103.0867569444363</v>
-      </c>
-      <c r="P74" s="4" t="n">
-        <v>126.4197299966517</v>
+        <v>77.36466598240835</v>
       </c>
     </row>
     <row r="75">
@@ -14680,31 +13355,13 @@
         <v>39.50067776847708</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>9.959850795700929</v>
+        <v>64.83135362293784</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>10.26878513436696</v>
+        <v>70.32512884555851</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>11.33461677256776</v>
-      </c>
-      <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="n">
-        <v>4.376689796982279</v>
-      </c>
-      <c r="M75" s="4" t="n">
-        <v>9.600480844993342</v>
-      </c>
-      <c r="N75" s="4" t="n">
-        <v>85.50549898426496</v>
-      </c>
-      <c r="O75" s="4" t="n">
-        <v>102.7158792599473</v>
-      </c>
-      <c r="P75" s="4" t="n">
-        <v>126.2053150914379</v>
+        <v>77.05093838237508</v>
       </c>
     </row>
     <row r="76">
@@ -14730,31 +13387,13 @@
         <v>39.70035829830983</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>9.989516653289776</v>
+        <v>64.27840510875224</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>10.17932218854736</v>
+        <v>69.73068736197234</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>11.26555539540986</v>
-      </c>
-      <c r="K76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="4" t="n">
-        <v>4.376689796982279</v>
-      </c>
-      <c r="M76" s="4" t="n">
-        <v>9.600480844993342</v>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v>84.93550920442941</v>
-      </c>
-      <c r="O76" s="4" t="n">
-        <v>101.9448445584105</v>
-      </c>
-      <c r="P76" s="4" t="n">
-        <v>125.5317820439188</v>
+        <v>76.40967971411388</v>
       </c>
     </row>
     <row r="77">
@@ -14780,31 +13419,13 @@
         <v>40.90756460332478</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>9.921400645660905</v>
+        <v>64.44335394151142</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10.11629299804721</v>
+        <v>70.12243333580332</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>11.14843758270352</v>
-      </c>
-      <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v>4.407908768095036</v>
-      </c>
-      <c r="M77" s="4" t="n">
-        <v>9.668961168724614</v>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v>85.14973811225101</v>
-      </c>
-      <c r="O77" s="4" t="n">
-        <v>102.3282306305521</v>
-      </c>
-      <c r="P77" s="4" t="n">
-        <v>126.0152100206047</v>
+        <v>77.08321264462366</v>
       </c>
     </row>
     <row r="78">
@@ -14830,31 +13451,13 @@
         <v>41.8250523841525</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>9.85462026906597</v>
+        <v>63.91923188012164</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10.07669717785873</v>
+        <v>69.68432686452016</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>11.06804053509465</v>
-      </c>
-      <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v>4.43629765474369</v>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v>9.731233565244242</v>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v>84.59361419859319</v>
-      </c>
-      <c r="O78" s="4" t="n">
-        <v>101.9070725406245</v>
-      </c>
-      <c r="P78" s="4" t="n">
-        <v>125.6927274253359</v>
+        <v>76.74343773513553</v>
       </c>
     </row>
     <row r="79">
@@ -14880,31 +13483,13 @@
         <v>42.64544430053726</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>9.923164692080082</v>
+        <v>64.38564985063125</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>10.14524160087284</v>
+        <v>70.30704609914129</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>11.14557957692266</v>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v>4.3170223446876</v>
-      </c>
-      <c r="M79" s="4" t="n">
-        <v>9.469597401250228</v>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v>85.1278250920809</v>
-      </c>
-      <c r="O79" s="4" t="n">
-        <v>102.5222426071771</v>
-      </c>
-      <c r="P79" s="4" t="n">
-        <v>125.712473346676</v>
+        <v>77.55286472444182</v>
       </c>
     </row>
     <row r="80">
@@ -14930,31 +13515,13 @@
         <v>42.75390434460453</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>9.923879113397142</v>
+        <v>62.87758572779481</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>10.08845062412284</v>
+        <v>68.81893706830294</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>11.11551387247879</v>
-      </c>
-      <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="4" t="n">
-        <v>4.435073100864514</v>
-      </c>
-      <c r="M80" s="4" t="n">
-        <v>9.728547447057649</v>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v>83.61976096924447</v>
-      </c>
-      <c r="O80" s="4" t="n">
-        <v>101.0946789344486</v>
-      </c>
-      <c r="P80" s="4" t="n">
-        <v>124.4757422550684</v>
+        <v>76.08796371278771</v>
       </c>
     </row>
     <row r="81">
@@ -14980,31 +13547,13 @@
         <v>42.94647852938239</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>10.07211708290364</v>
+        <v>63.10209722603607</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>10.26214447152228</v>
+        <v>69.0736549083617</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>11.31115190667997</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v>4.454206234247971</v>
-      </c>
-      <c r="M81" s="4" t="n">
-        <v>9.770516900931035</v>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v>83.99814704582117</v>
-      </c>
-      <c r="O81" s="4" t="n">
-        <v>101.5525300925287</v>
-      </c>
-      <c r="P81" s="4" t="n">
-        <v>125.5382614426951</v>
+        <v>76.37870467321727</v>
       </c>
     </row>
     <row r="82">
@@ -15030,31 +13579,13 @@
         <v>42.94647852938239</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>10.12344865465414</v>
+        <v>60.81101774421572</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>10.31174224762866</v>
+        <v>66.78257542654136</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>11.42511970067767</v>
-      </c>
-      <c r="K82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v>4.473141716752077</v>
-      </c>
-      <c r="M82" s="4" t="n">
-        <v>9.812052798036817</v>
-      </c>
-      <c r="N82" s="4" t="n">
-        <v>81.76760716666961</v>
-      </c>
-      <c r="O82" s="4" t="n">
-        <v>99.45192503133312</v>
-      </c>
-      <c r="P82" s="4" t="n">
-        <v>123.5880375191989</v>
+        <v>74.08762519139694</v>
       </c>
     </row>
     <row r="83">
@@ -15080,31 +13611,13 @@
         <v>43.72936837404508</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>10.13146678488303</v>
+        <v>61.14797386186072</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10.32768622625903</v>
+        <v>67.1770707028379</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>11.4431444224329</v>
-      </c>
-      <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v>4.477435105244823</v>
-      </c>
-      <c r="M83" s="4" t="n">
-        <v>9.821470553440262</v>
-      </c>
-      <c r="N83" s="4" t="n">
-        <v>82.10456328431459</v>
-      </c>
-      <c r="O83" s="4" t="n">
-        <v>99.8507136961224</v>
-      </c>
-      <c r="P83" s="4" t="n">
-        <v>124.0738543988567</v>
+        <v>74.56402431565134</v>
       </c>
     </row>
     <row r="84">
@@ -15130,31 +13643,13 @@
         <v>43.72936837404508</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>10.15105519239527</v>
+        <v>61.06436989102075</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>10.3481183229087</v>
+        <v>67.09346673199792</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>11.47791186809465</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="4" t="n">
-        <v>4.459210634102335</v>
-      </c>
-      <c r="M84" s="4" t="n">
-        <v>9.78149429415995</v>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v>82.03279712134433</v>
-      </c>
-      <c r="O84" s="4" t="n">
-        <v>99.755858098242</v>
-      </c>
-      <c r="P84" s="4" t="n">
-        <v>124.0892004525552</v>
+        <v>74.48042034481136</v>
       </c>
     </row>
     <row r="85">
@@ -15180,31 +13675,13 @@
         <v>43.39518616155637</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>10.18102656851889</v>
+        <v>58.72574161233486</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>10.41985970062598</v>
+        <v>64.80912915542287</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>11.50024460526566</v>
-      </c>
-      <c r="K85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="4" t="n">
-        <v>4.459210634102335</v>
-      </c>
-      <c r="M85" s="4" t="n">
-        <v>9.78149429415995</v>
-      </c>
-      <c r="N85" s="4" t="n">
-        <v>80.04469345667874</v>
-      </c>
-      <c r="O85" s="4" t="n">
-        <v>98.11009318399528</v>
-      </c>
-      <c r="P85" s="4" t="n">
-        <v>122.3415891005228</v>
+        <v>72.24973951768067</v>
       </c>
     </row>
     <row r="86">
@@ -15230,31 +13707,13 @@
         <v>44.18838625474493</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>10.45134176282593</v>
+        <v>59.10066580773176</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10.7268004299584</v>
+        <v>65.41072559787821</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>11.69796567554046</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v>4.345173242862129</v>
-      </c>
-      <c r="M86" s="4" t="n">
-        <v>9.531347758536279</v>
-      </c>
-      <c r="N86" s="4" t="n">
-        <v>80.70568849717877</v>
-      </c>
-      <c r="O86" s="4" t="n">
-        <v>99.87379345323558</v>
-      </c>
-      <c r="P86" s="4" t="n">
-        <v>125.3812181735379</v>
+        <v>73.08300371254009</v>
       </c>
     </row>
     <row r="87">
@@ -15280,31 +13739,13 @@
         <v>42.27639445908945</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>10.5784627835235</v>
+        <v>58.41417782741178</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>10.86555729328646</v>
+        <v>64.25366465383183</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>11.9999124072767</v>
-      </c>
-      <c r="K87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="4" t="n">
-        <v>3.827627549249396</v>
-      </c>
-      <c r="M87" s="4" t="n">
-        <v>8.396086237063178</v>
-      </c>
-      <c r="N87" s="4" t="n">
-        <v>80.220071638145</v>
-      </c>
-      <c r="O87" s="4" t="n">
-        <v>98.3847177293426</v>
-      </c>
-      <c r="P87" s="4" t="n">
-        <v>122.7748259550807</v>
+        <v>71.39154547507607</v>
       </c>
     </row>
     <row r="88">
@@ -15330,31 +13771,13 @@
         <v>42.43313177156649</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>11.22644695296166</v>
+        <v>58.61488048674104</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>11.54252613034671</v>
+        <v>64.47015547469498</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>12.67112389654174</v>
-      </c>
-      <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="4" t="n">
-        <v>3.638739652811751</v>
-      </c>
-      <c r="M88" s="4" t="n">
-        <v>7.981751496490272</v>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v>80.84289544625497</v>
-      </c>
-      <c r="O88" s="4" t="n">
-        <v>98.7050128699408</v>
-      </c>
-      <c r="P88" s="4" t="n">
-        <v>124.1028102775291</v>
+        <v>71.6292703608172</v>
       </c>
     </row>
     <row r="89">
@@ -15380,31 +13803,13 @@
         <v>42.90894863463689</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>11.3899272945248</v>
+        <v>60.48522905216423</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11.72590185893684</v>
+        <v>66.43197231417088</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>12.8933913175205</v>
-      </c>
-      <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v>3.66393328095797</v>
-      </c>
-      <c r="M89" s="4" t="n">
-        <v>8.037014938875526</v>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v>83.31371477831598</v>
-      </c>
-      <c r="O89" s="4" t="n">
-        <v>101.3468561431619</v>
-      </c>
-      <c r="P89" s="4" t="n">
-        <v>127.0913614623047</v>
+        <v>73.68409341090734</v>
       </c>
     </row>
     <row r="90">
@@ -15430,31 +13835,13 @@
         <v>43.00567499864871</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>11.52484311861287</v>
+        <v>61.62995734512003</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>11.87358008125339</v>
+        <v>67.59500249679519</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>13.06510866441957</v>
-      </c>
-      <c r="K90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="4" t="n">
-        <v>3.354511937034389</v>
-      </c>
-      <c r="M90" s="4" t="n">
-        <v>7.358284248978659</v>
-      </c>
-      <c r="N90" s="4" t="n">
-        <v>84.46364548072162</v>
-      </c>
-      <c r="O90" s="4" t="n">
-        <v>102.2258860246433</v>
-      </c>
-      <c r="P90" s="4" t="n">
-        <v>127.7761815096178</v>
+        <v>74.90867515214893</v>
       </c>
     </row>
     <row r="91">
@@ -15480,31 +13867,13 @@
         <v>43.02749770450217</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>11.28890500635013</v>
+        <v>61.94162567895114</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>11.63949478014972</v>
+        <v>67.92105130659544</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>12.88624640631504</v>
-      </c>
-      <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="4" t="n">
-        <v>3.354511937034389</v>
-      </c>
-      <c r="M91" s="4" t="n">
-        <v>7.358284248978659</v>
-      </c>
-      <c r="N91" s="4" t="n">
-        <v>84.53148206360413</v>
-      </c>
-      <c r="O91" s="4" t="n">
-        <v>102.1943001201383</v>
-      </c>
-      <c r="P91" s="4" t="n">
-        <v>127.1977312278448</v>
+        <v>75.23783138774328</v>
       </c>
     </row>
     <row r="92">
@@ -15530,31 +13899,13 @@
         <v>43.69323648032401</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>11.24844901910896</v>
+        <v>62.42049813526873</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>11.54168249029665</v>
+        <v>68.69049566484321</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>12.69538346139267</v>
-      </c>
-      <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="4" t="n">
-        <v>3.493586280018454</v>
-      </c>
-      <c r="M92" s="4" t="n">
-        <v>7.663350549717899</v>
-      </c>
-      <c r="N92" s="4" t="n">
-        <v>85.03770206212026</v>
-      </c>
-      <c r="O92" s="4" t="n">
-        <v>102.8489608159495</v>
-      </c>
-      <c r="P92" s="4" t="n">
-        <v>127.8001111604239</v>
+        <v>76.05686929621442</v>
       </c>
     </row>
     <row r="93">
@@ -15580,31 +13931,13 @@
         <v>43.81838416151118</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>11.12090121960202</v>
+        <v>63.70979083629432</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11.44545578714944</v>
+        <v>69.78728870383338</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>12.78119633702218</v>
-      </c>
-      <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v>3.566643807665413</v>
-      </c>
-      <c r="M93" s="4" t="n">
-        <v>7.823605771653171</v>
-      </c>
-      <c r="N93" s="4" t="n">
-        <v>86.24274901093219</v>
-      </c>
-      <c r="O93" s="4" t="n">
-        <v>104.0533240144436</v>
-      </c>
-      <c r="P93" s="4" t="n">
-        <v>129.0580994564493</v>
+        <v>77.20886881704412</v>
       </c>
     </row>
     <row r="94">
@@ -15630,31 +13963,13 @@
         <v>43.89383563730097</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>11.45708290130502</v>
+        <v>64.59670493498584</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>11.83146849556317</v>
+        <v>70.65509225594184</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>13.2180085821196</v>
-      </c>
-      <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="n">
-        <v>3.590705116214214</v>
-      </c>
-      <c r="M94" s="4" t="n">
-        <v>7.876385416211837</v>
-      </c>
-      <c r="N94" s="4" t="n">
-        <v>87.62028979709285</v>
-      </c>
-      <c r="O94" s="4" t="n">
-        <v>105.9667668700174</v>
-      </c>
-      <c r="P94" s="4" t="n">
-        <v>131.6697921526543</v>
+        <v>78.11413343233505</v>
       </c>
     </row>
     <row r="95">
@@ -15680,31 +13995,13 @@
         <v>44.18942166763616</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>11.49533685767401</v>
+        <v>69.47328952655317</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>11.78040637051136</v>
+        <v>75.50823288476769</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>13.07726310365784</v>
-      </c>
-      <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="n">
-        <v>3.651625772652042</v>
-      </c>
-      <c r="M95" s="4" t="n">
-        <v>8.010017823881913</v>
-      </c>
-      <c r="N95" s="4" t="n">
-        <v>92.51433783561224</v>
-      </c>
-      <c r="O95" s="4" t="n">
-        <v>110.8064380109314</v>
-      </c>
-      <c r="P95" s="4" t="n">
-        <v>136.8073360861565</v>
+        <v>83.25112019544326</v>
       </c>
     </row>
     <row r="96">
@@ -15730,31 +14027,13 @@
         <v>44.19775822053433</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>11.50810423319403</v>
+        <v>71.08120460799201</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>11.8011441045994</v>
+        <v>77.14076078430308</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>13.10532483569728</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="4" t="n">
-        <v>3.671906780074722</v>
-      </c>
-      <c r="M96" s="4" t="n">
-        <v>8.05450519500263</v>
-      </c>
-      <c r="N96" s="4" t="n">
-        <v>94.2325070529147</v>
-      </c>
-      <c r="O96" s="4" t="n">
-        <v>112.5988134625233</v>
-      </c>
-      <c r="P96" s="4" t="n">
-        <v>138.5068991802361</v>
+        <v>84.65028428203101</v>
       </c>
     </row>
     <row r="97">
@@ -15780,31 +14059,13 @@
         <v>44.9093869047366</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>11.36269257415815</v>
+        <v>73.37469572233228</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>11.6961560986665</v>
+        <v>79.50447232392906</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>13.10532483569728</v>
-      </c>
-      <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>3.704961315258361</v>
-      </c>
-      <c r="M97" s="4" t="n">
-        <v>8.127011917340935</v>
-      </c>
-      <c r="N97" s="4" t="n">
-        <v>96.3919869000154</v>
-      </c>
-      <c r="O97" s="4" t="n">
-        <v>114.9216868566642</v>
-      </c>
-      <c r="P97" s="4" t="n">
-        <v>141.234610321904</v>
+        <v>87.0771309049945</v>
       </c>
     </row>
     <row r="98">
@@ -15830,31 +14091,13 @@
         <v>45.43373434088954</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>11.31108453192815</v>
+        <v>73.72207398198313</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>11.61291457879188</v>
+        <v>79.98125202361462</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>13.17122480693359</v>
-      </c>
-      <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="4" t="n">
-        <v>3.716761624866966</v>
-      </c>
-      <c r="M98" s="4" t="n">
-        <v>8.15289646745013</v>
-      </c>
-      <c r="N98" s="4" t="n">
-        <v>96.6545679794512</v>
-      </c>
-      <c r="O98" s="4" t="n">
-        <v>115.623161131077</v>
-      </c>
-      <c r="P98" s="4" t="n">
-        <v>142.0336095068545</v>
+        <v>87.60147834114744</v>
       </c>
     </row>
     <row r="99">
@@ -15880,31 +14123,13 @@
         <v>45.9921403012924</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>11.2970857672083</v>
+        <v>74.17684112303807</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>11.64395578988422</v>
+        <v>80.44918839896171</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>13.17066170667912</v>
-      </c>
-      <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="n">
-        <v>3.732079939233118</v>
-      </c>
-      <c r="M99" s="4" t="n">
-        <v>8.186497931221046</v>
-      </c>
-      <c r="N99" s="4" t="n">
-        <v>97.15165191781423</v>
-      </c>
-      <c r="O99" s="4" t="n">
-        <v>116.3031801240757</v>
-      </c>
-      <c r="P99" s="4" t="n">
-        <v>143.1118645698257</v>
+        <v>88.15988430155031</v>
       </c>
     </row>
     <row r="100">
@@ -15930,31 +14155,13 @@
         <v>46.00398530516502</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>11.38747751273552</v>
+        <v>75.80950832814175</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>11.74628427347466</v>
+        <v>82.09102375643793</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>13.27845710875297</v>
-      </c>
-      <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="n">
-        <v>3.812508707855299</v>
-      </c>
-      <c r="M100" s="4" t="n">
-        <v>8.362922326908398</v>
-      </c>
-      <c r="N100" s="4" t="n">
-        <v>98.89318659145177</v>
-      </c>
-      <c r="O100" s="4" t="n">
-        <v>118.1776348896867</v>
-      </c>
-      <c r="P100" s="4" t="n">
-        <v>145.1438353780881</v>
+        <v>89.79785721130344</v>
       </c>
     </row>
     <row r="101">
@@ -15980,31 +14187,13 @@
         <v>46.03041463755706</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>11.39006105768579</v>
+        <v>76.86637164166166</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>11.74815216774377</v>
+        <v>83.13311139754293</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>13.30132943543884</v>
-      </c>
-      <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="n">
-        <v>3.989497132653419</v>
-      </c>
-      <c r="M101" s="4" t="n">
-        <v>8.751155000659134</v>
-      </c>
-      <c r="N101" s="4" t="n">
-        <v>100.1482543778411</v>
-      </c>
-      <c r="O101" s="4" t="n">
-        <v>119.4804400307067</v>
-      </c>
-      <c r="P101" s="4" t="n">
-        <v>146.7267599128649</v>
+        <v>90.85090362721914</v>
       </c>
     </row>
     <row r="102">
@@ -16030,31 +14219,13 @@
         <v>46.06090251530795</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>11.46696428605146</v>
+        <v>79.35033570789287</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>11.82686100737961</v>
+        <v>85.59195928426726</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>13.43795366851972</v>
-      </c>
-      <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="n">
-        <v>3.99508853012664</v>
-      </c>
-      <c r="M102" s="4" t="n">
-        <v>8.763420001568138</v>
-      </c>
-      <c r="N102" s="4" t="n">
-        <v>102.8019338770712</v>
-      </c>
-      <c r="O102" s="4" t="n">
-        <v>122.1058427346521</v>
-      </c>
-      <c r="P102" s="4" t="n">
-        <v>149.6354440672185</v>
+        <v>93.25237532242873</v>
       </c>
     </row>
     <row r="103">
@@ -16080,31 +14251,13 @@
         <v>51.12935092145549</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>11.87500039258757</v>
+        <v>85.32846449281341</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>12.24457307209753</v>
+        <v>92.20127673701586</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>13.83096553935464</v>
-      </c>
-      <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="4" t="n">
-        <v>4.136678825370385</v>
-      </c>
-      <c r="M103" s="4" t="n">
-        <v>9.074005165328559</v>
-      </c>
-      <c r="N103" s="4" t="n">
-        <v>111.1520090455139</v>
-      </c>
-      <c r="O103" s="4" t="n">
-        <v>132.3512222357217</v>
-      </c>
-      <c r="P103" s="4" t="n">
-        <v>161.7572232863249</v>
+        <v>100.6412912952821</v>
       </c>
     </row>
     <row r="104">
@@ -16130,31 +14283,13 @@
         <v>52.3396006714277</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>11.85451883177122</v>
+        <v>89.1566575789351</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>12.21636323514575</v>
+        <v>96.19704289699415</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>14.22960009805919</v>
-      </c>
-      <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="4" t="n">
-        <v>4.491732143853754</v>
-      </c>
-      <c r="M104" s="4" t="n">
-        <v>9.8528317994211</v>
-      </c>
-      <c r="N104" s="4" t="n">
-        <v>115.155933378555</v>
-      </c>
-      <c r="O104" s="4" t="n">
-        <v>137.436243315793</v>
-      </c>
-      <c r="P104" s="4" t="n">
-        <v>168.43516242816</v>
+        <v>104.8389354907997</v>
       </c>
     </row>
     <row r="105">
@@ -16180,31 +14315,13 @@
         <v>50.70866037908584</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>11.74169268031328</v>
+        <v>99.13426022547468</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>12.04844665078395</v>
+        <v>105.9737073033593</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>13.63286033164314</v>
-      </c>
-      <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="4" t="n">
-        <v>4.508171632986699</v>
-      </c>
-      <c r="M105" s="4" t="n">
-        <v>9.888892614293368</v>
-      </c>
-      <c r="N105" s="4" t="n">
-        <v>125.1860041739226</v>
-      </c>
-      <c r="O105" s="4" t="n">
-        <v>147.2963707514735</v>
-      </c>
-      <c r="P105" s="4" t="n">
-        <v>177.648024554089</v>
+        <v>114.3444976215707</v>
       </c>
     </row>
     <row r="106">
@@ -16230,31 +14347,13 @@
         <v>50.24496936363312</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>11.80506636025897</v>
+        <v>103.7943748957108</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>12.10897915051754</v>
+        <v>110.5153312465385</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>13.6917200506369</v>
-      </c>
-      <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="n">
-        <v>4.536512620598686</v>
-      </c>
-      <c r="M106" s="4" t="n">
-        <v>9.951059941958375</v>
-      </c>
-      <c r="N106" s="4" t="n">
-        <v>130.019023672655</v>
-      </c>
-      <c r="O106" s="4" t="n">
-        <v>152.2820183311484</v>
-      </c>
-      <c r="P106" s="4" t="n">
-        <v>181.6596053915836</v>
+        <v>118.7678202802275</v>
       </c>
     </row>
     <row r="107">
@@ -16280,31 +14379,13 @@
         <v>49.70920524993808</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>11.97697397020622</v>
+        <v>110.9741582559974</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>12.2857009915681</v>
+        <v>117.7335787202798</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>13.87652009179157</v>
-      </c>
-      <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="n">
-        <v>4.58027403594367</v>
-      </c>
-      <c r="M107" s="4" t="n">
-        <v>10.04705272400543</v>
-      </c>
-      <c r="N107" s="4" t="n">
-        <v>137.2404373134675</v>
-      </c>
-      <c r="O107" s="4" t="n">
-        <v>159.5784105733883</v>
-      </c>
-      <c r="P107" s="4" t="n">
-        <v>189.0271557814123</v>
+        <v>125.9791312052712</v>
       </c>
     </row>
     <row r="108">
@@ -16330,31 +14411,13 @@
         <v>49.91126651609233</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>12.05848709683931</v>
+        <v>116.0293886220061</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12.3637703862784</v>
+        <v>122.7902530202565</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>13.92624639538636</v>
-      </c>
-      <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="n">
-        <v>4.67687719159351</v>
-      </c>
-      <c r="M108" s="4" t="n">
-        <v>10.2589564202696</v>
-      </c>
-      <c r="N108" s="4" t="n">
-        <v>142.4226509745124</v>
-      </c>
-      <c r="O108" s="4" t="n">
-        <v>164.8886732457904</v>
-      </c>
-      <c r="P108" s="4" t="n">
-        <v>194.4484429041176</v>
+        <v>131.0449611657389</v>
       </c>
     </row>
     <row r="109">
@@ -16380,31 +14443,13 @@
         <v>49.35545684805921</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>12.05848912053451</v>
+        <v>119.8241849274356</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>12.37521247493388</v>
+        <v>126.3477492013446</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>13.94140733637457</v>
-      </c>
-      <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="n">
-        <v>4.67687719159351</v>
-      </c>
-      <c r="M109" s="4" t="n">
-        <v>10.2589564202696</v>
-      </c>
-      <c r="N109" s="4" t="n">
-        <v>146.2174472799419</v>
-      </c>
-      <c r="O109" s="4" t="n">
-        <v>168.4461694268785</v>
-      </c>
-      <c r="P109" s="4" t="n">
-        <v>197.7790557962712</v>
+        <v>134.3755740578925</v>
       </c>
     </row>
     <row r="110">
@@ -16430,31 +14475,13 @@
         <v>49.35545684805921</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>12.0167719588689</v>
+        <v>126.1303175799407</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>12.33349531326828</v>
+        <v>132.6538818538497</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>13.89969017470896</v>
-      </c>
-      <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="n">
-        <v>4.662637056304053</v>
-      </c>
-      <c r="M110" s="4" t="n">
-        <v>10.22771999447339</v>
-      </c>
-      <c r="N110" s="4" t="n">
-        <v>152.4094051737834</v>
-      </c>
-      <c r="O110" s="4" t="n">
-        <v>174.6338565693593</v>
-      </c>
-      <c r="P110" s="4" t="n">
-        <v>203.9919256664637</v>
+        <v>140.6817067103976</v>
       </c>
     </row>
     <row r="111">
@@ -16480,31 +14507,13 @@
         <v>49.35545684805921</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>11.9003580906755</v>
+        <v>126.1797863147918</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>12.20564138011459</v>
+        <v>132.7033505887007</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>13.78544494798415</v>
-      </c>
-      <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="4" t="n">
-        <v>4.648950235422728</v>
-      </c>
-      <c r="M111" s="4" t="n">
-        <v>10.1976972906047</v>
-      </c>
-      <c r="N111" s="4" t="n">
-        <v>152.4044350917359</v>
-      </c>
-      <c r="O111" s="4" t="n">
-        <v>174.6382693038806</v>
-      </c>
-      <c r="P111" s="4" t="n">
-        <v>204.1074974569275</v>
+        <v>140.7311754452486</v>
       </c>
     </row>
     <row r="112">
@@ -16530,31 +14539,13 @@
         <v>49.31327569013229</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>11.81893386887723</v>
+        <v>125.3224647993997</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>12.12766089023911</v>
+        <v>131.951157013991</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>13.787829688819</v>
-      </c>
-      <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="4" t="n">
-        <v>4.590922511646566</v>
-      </c>
-      <c r="M112" s="4" t="n">
-        <v>10.07041067070862</v>
-      </c>
-      <c r="N112" s="4" t="n">
-        <v>151.5014862348844</v>
-      </c>
-      <c r="O112" s="4" t="n">
-        <v>173.7664535795311</v>
-      </c>
-      <c r="P112" s="4" t="n">
-        <v>203.5125910707293</v>
+        <v>140.1048281000096</v>
       </c>
     </row>
     <row r="113">
@@ -16580,31 +14571,13 @@
         <v>49.67609518737975</v>
       </c>
       <c r="H113" s="4" t="n">
-        <v>11.9047987607091</v>
+        <v>125.7740217217115</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>12.26025055411113</v>
+        <v>132.4647436005064</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>13.787829688819</v>
-      </c>
-      <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="n">
-        <v>4.6110319036</v>
-      </c>
-      <c r="M113" s="4" t="n">
-        <v>10.11452159499348</v>
-      </c>
-      <c r="N113" s="4" t="n">
-        <v>151.7988434645977</v>
-      </c>
-      <c r="O113" s="4" t="n">
-        <v>174.4635423576335</v>
-      </c>
-      <c r="P113" s="4" t="n">
-        <v>204.4957313968927</v>
+        <v>140.6959142116292</v>
       </c>
     </row>
     <row r="114">
@@ -16630,31 +14603,13 @@
         <v>49.95054060305937</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>11.81468148593934</v>
+        <v>126.6140991405551</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>12.15431627887534</v>
+        <v>133.3680253953266</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>13.46832626916193</v>
-      </c>
-      <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4" t="n">
-        <v>4.583673317217324</v>
-      </c>
-      <c r="M114" s="4" t="n">
-        <v>10.05450921196056</v>
-      </c>
-      <c r="N114" s="4" t="n">
-        <v>152.1756918457187</v>
-      </c>
-      <c r="O114" s="4" t="n">
-        <v>173.6978781942601</v>
-      </c>
-      <c r="P114" s="4" t="n">
-        <v>203.774228366781</v>
+        <v>141.5559749779131</v>
       </c>
     </row>
     <row r="115">
@@ -16680,31 +14635,13 @@
         <v>50.06947831360792</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>11.15185472275178</v>
+        <v>124.6524793581307</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>11.42085946435819</v>
+        <v>131.4064056129022</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>12.76825008635148</v>
-      </c>
-      <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="4" t="n">
-        <v>4.663484969361968</v>
-      </c>
-      <c r="M115" s="4" t="n">
-        <v>10.22957993279398</v>
-      </c>
-      <c r="N115" s="4" t="n">
-        <v>149.4217310623142</v>
-      </c>
-      <c r="O115" s="4" t="n">
-        <v>170.253575238876</v>
-      </c>
-      <c r="P115" s="4" t="n">
-        <v>198.0371685193943</v>
+        <v>139.7132929060372</v>
       </c>
     </row>
     <row r="116">
@@ -16730,31 +14667,13 @@
         <v>50.06947831360792</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>11.23197702341489</v>
+        <v>123.1677976005264</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>11.54429584518954</v>
+        <v>129.9217238552978</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>12.86735688879075</v>
-      </c>
-      <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="4" t="n">
-        <v>4.812647309396379</v>
-      </c>
-      <c r="M116" s="4" t="n">
-        <v>10.55677474319208</v>
-      </c>
-      <c r="N116" s="4" t="n">
-        <v>148.0146791231456</v>
-      </c>
-      <c r="O116" s="4" t="n">
-        <v>169.0379710327817</v>
-      </c>
-      <c r="P116" s="4" t="n">
-        <v>197.2205095263856</v>
+        <v>138.2286111484329</v>
       </c>
     </row>
     <row r="117">
@@ -16780,31 +14699,13 @@
         <v>50.06947831360792</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>11.32357303274463</v>
+        <v>123.0229969986563</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>11.62074269811992</v>
+        <v>129.7769232534277</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>12.93478842344754</v>
-      </c>
-      <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="4" t="n">
-        <v>5.159160924608611</v>
-      </c>
-      <c r="M117" s="4" t="n">
-        <v>11.31686912494793</v>
-      </c>
-      <c r="N117" s="4" t="n">
-        <v>147.961943452596</v>
-      </c>
-      <c r="O117" s="4" t="n">
-        <v>169.2794311644923</v>
-      </c>
-      <c r="P117" s="4" t="n">
-        <v>197.8240512886422</v>
+        <v>138.0838105465628</v>
       </c>
     </row>
     <row r="118">
@@ -16830,31 +14731,13 @@
         <v>50.06947831360792</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>11.10360018111531</v>
+        <v>121.5668712072758</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>11.37942896799853</v>
+        <v>128.3207974620472</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>12.74446988193458</v>
-      </c>
-      <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="4" t="n">
-        <v>5.159160924608611</v>
-      </c>
-      <c r="M118" s="4" t="n">
-        <v>11.31686912494793</v>
-      </c>
-      <c r="N118" s="4" t="n">
-        <v>146.3416723107103</v>
-      </c>
-      <c r="O118" s="4" t="n">
-        <v>167.6367904569861</v>
-      </c>
-      <c r="P118" s="4" t="n">
-        <v>196.1850221364423</v>
+        <v>136.6276847551823</v>
       </c>
     </row>
     <row r="119">
@@ -16880,31 +14763,13 @@
         <v>50.31871818702958</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>11.09581217230755</v>
+        <v>121.6772582759922</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>11.36300564534352</v>
+        <v>128.4601082861814</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>12.7144110549298</v>
-      </c>
-      <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="n">
-        <v>4.970803246785806</v>
-      </c>
-      <c r="M119" s="4" t="n">
-        <v>10.90369744456239</v>
-      </c>
-      <c r="N119" s="4" t="n">
-        <v>146.6272687563258</v>
-      </c>
-      <c r="O119" s="4" t="n">
-        <v>167.363695684642</v>
-      </c>
-      <c r="P119" s="4" t="n">
-        <v>195.8524379622795</v>
+        <v>136.8067691024968</v>
       </c>
     </row>
     <row r="120">
@@ -16930,31 +14795,13 @@
         <v>50.49511498374005</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>11.05392598392102</v>
+        <v>120.0641981735216</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>11.31417680693295</v>
+        <v>126.8746990270803</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>12.67103169071429</v>
-      </c>
-      <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="4" t="n">
-        <v>4.971718678720381</v>
-      </c>
-      <c r="M120" s="4" t="n">
-        <v>10.90570548880598</v>
-      </c>
-      <c r="N120" s="4" t="n">
-        <v>145.1403481328081</v>
-      </c>
-      <c r="O120" s="4" t="n">
-        <v>165.7488975498133</v>
-      </c>
-      <c r="P120" s="4" t="n">
-        <v>194.0279806093808</v>
+        <v>135.2491196357905</v>
       </c>
     </row>
     <row r="121">
@@ -16980,31 +14827,13 @@
         <v>50.50070046663136</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>10.99548125129088</v>
+        <v>118.7857734748556</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>11.24740238955052</v>
+        <v>125.5899594154016</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>12.63120974759281</v>
-      </c>
-      <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="4" t="n">
-        <v>5.19523790386538</v>
-      </c>
-      <c r="M121" s="4" t="n">
-        <v>11.39600572460791</v>
-      </c>
-      <c r="N121" s="4" t="n">
-        <v>143.7704392106932</v>
-      </c>
-      <c r="O121" s="4" t="n">
-        <v>164.4755071599075</v>
-      </c>
-      <c r="P121" s="4" t="n">
-        <v>193.0184435701647</v>
+        <v>133.9674810345183</v>
       </c>
     </row>
     <row r="122">
@@ -17030,31 +14859,13 @@
         <v>51.14161909967719</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>10.87806460384366</v>
+        <v>117.1675912266219</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>11.14638473306776</v>
+        <v>124.0622883572165</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>12.46452656766012</v>
-      </c>
-      <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="4" t="n">
-        <v>5.341001643431349</v>
-      </c>
-      <c r="M122" s="4" t="n">
-        <v>11.71574554043004</v>
-      </c>
-      <c r="N122" s="4" t="n">
-        <v>142.2939613355455</v>
-      </c>
-      <c r="O122" s="4" t="n">
-        <v>163.1546395243582</v>
-      </c>
-      <c r="P122" s="4" t="n">
-        <v>191.9106307375301</v>
+        <v>132.5487783363216</v>
       </c>
     </row>
     <row r="123">
@@ -17080,31 +14891,13 @@
         <v>54.11183635524702</v>
       </c>
       <c r="H123" s="4" t="n">
-        <v>10.87040942187155</v>
+        <v>116.8277677619608</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>11.14623485535493</v>
+        <v>124.1463625841027</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>12.4758249429248</v>
-      </c>
-      <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="4" t="n">
-        <v>5.233788291213194</v>
-      </c>
-      <c r="M123" s="4" t="n">
-        <v>11.48056786459662</v>
-      </c>
-      <c r="N123" s="4" t="n">
-        <v>143.0615632194848</v>
-      </c>
-      <c r="O123" s="4" t="n">
-        <v>162.6732595335574</v>
-      </c>
-      <c r="P123" s="4" t="n">
-        <v>191.5659393722142</v>
+        <v>133.1551548768026</v>
       </c>
     </row>
     <row r="124">
@@ -17130,31 +14923,13 @@
         <v>61.05859019012696</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>10.53829856258206</v>
+        <v>119.9676079504722</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10.77733235026552</v>
+        <v>128.2180719213364</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>11.93848113637809</v>
-      </c>
-      <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="4" t="n">
-        <v>5.214558854900471</v>
-      </c>
-      <c r="M124" s="4" t="n">
-        <v>11.43838716558813</v>
-      </c>
-      <c r="N124" s="4" t="n">
-        <v>148.0269955766626</v>
-      </c>
-      <c r="O124" s="4" t="n">
-        <v>169.019431250698</v>
-      </c>
-      <c r="P124" s="4" t="n">
-        <v>197.5249504899924</v>
+        <v>138.3780516393196</v>
       </c>
     </row>
     <row r="125">
@@ -17180,31 +14955,13 @@
         <v>61.22288398033616</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>10.55161039907249</v>
+        <v>114.8496539541184</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>10.7885519162505</v>
+        <v>123.127932607511</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>11.89627916963101</v>
-      </c>
-      <c r="K125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="4" t="n">
-        <v>5.363929370940968</v>
-      </c>
-      <c r="M125" s="4" t="n">
-        <v>11.76603862012857</v>
-      </c>
-      <c r="N125" s="4" t="n">
-        <v>143.0089640876067</v>
-      </c>
-      <c r="O125" s="4" t="n">
-        <v>164.1795874473553</v>
-      </c>
-      <c r="P125" s="4" t="n">
-        <v>191.7561701821453</v>
+        <v>133.3192910099003</v>
       </c>
     </row>
     <row r="126">
@@ -17230,31 +14987,13 @@
         <v>62.68718141071901</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>10.58089511644547</v>
+        <v>100.6543532677092</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>10.81783663362348</v>
+        <v>109.1254530315072</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>11.92556388700399</v>
-      </c>
-      <c r="K126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="4" t="n">
-        <v>5.543792561577728</v>
-      </c>
-      <c r="M126" s="4" t="n">
-        <v>12.16057723184792</v>
-      </c>
-      <c r="N126" s="4" t="n">
-        <v>129.3178942230936</v>
-      </c>
-      <c r="O126" s="4" t="n">
-        <v>150.756151765008</v>
-      </c>
-      <c r="P126" s="4" t="n">
-        <v>178.4895866786089</v>
+        <v>119.5517853568943</v>
       </c>
     </row>
     <row r="127">
@@ -17280,31 +15019,13 @@
         <v>62.93763105608939</v>
       </c>
       <c r="H127" s="4" t="n">
-        <v>10.62601693364672</v>
+        <v>99.88260940714746</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>10.85645706247544</v>
+        <v>108.4025822103398</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>11.84626514126893</v>
-      </c>
-      <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="4" t="n">
-        <v>5.547690783077972</v>
-      </c>
-      <c r="M127" s="4" t="n">
-        <v>12.16912816933232</v>
-      </c>
-      <c r="N127" s="4" t="n">
-        <v>128.7315974557343</v>
-      </c>
-      <c r="O127" s="4" t="n">
-        <v>150.4175319027296</v>
-      </c>
-      <c r="P127" s="4" t="n">
-        <v>178.2765852804631</v>
+        <v>118.8899176774786</v>
       </c>
     </row>
     <row r="128">
@@ -17330,31 +15051,13 @@
         <v>62.93763105608939</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>10.62903944113716</v>
+        <v>99.77522833188675</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>10.86598095831517</v>
+        <v>108.2952011350791</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>11.97370821169568</v>
-      </c>
-      <c r="K128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="4" t="n">
-        <v>5.658471056486826</v>
-      </c>
-      <c r="M128" s="4" t="n">
-        <v>12.41213005939046</v>
-      </c>
-      <c r="N128" s="4" t="n">
-        <v>128.6778719692969</v>
-      </c>
-      <c r="O128" s="4" t="n">
-        <v>150.4362687906229</v>
-      </c>
-      <c r="P128" s="4" t="n">
-        <v>178.9091480746316</v>
+        <v>118.7825366022179</v>
       </c>
     </row>
     <row r="129">
@@ -17380,31 +15083,13 @@
         <v>62.93763105608939</v>
       </c>
       <c r="H129" s="4" t="n">
-        <v>10.73033121235718</v>
+        <v>102.2659080537373</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>10.94213024589099</v>
+        <v>110.7858808569296</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>12.08831530870626</v>
-      </c>
-      <c r="K129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="4" t="n">
-        <v>5.694696307029685</v>
-      </c>
-      <c r="M129" s="4" t="n">
-        <v>12.49159189929092</v>
-      </c>
-      <c r="N129" s="4" t="n">
-        <v>131.207727661104</v>
-      </c>
-      <c r="O129" s="4" t="n">
-        <v>152.9686135904739</v>
-      </c>
-      <c r="P129" s="4" t="n">
-        <v>181.4792896363826</v>
+        <v>121.2732163240684</v>
       </c>
     </row>
     <row r="130">
@@ -17430,31 +15115,13 @@
         <v>62.93763105608939</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>10.94077424597496</v>
+        <v>109.3079001490731</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>11.11736069881739</v>
+        <v>117.8278729522655</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>12.22064533295436</v>
-      </c>
-      <c r="K130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="4" t="n">
-        <v>5.705411133724917</v>
-      </c>
-      <c r="M130" s="4" t="n">
-        <v>12.51509539010627</v>
-      </c>
-      <c r="N130" s="4" t="n">
-        <v>138.3737865114495</v>
-      </c>
-      <c r="O130" s="4" t="n">
-        <v>160.099633978348</v>
-      </c>
-      <c r="P130" s="4" t="n">
-        <v>188.6558483244949</v>
+        <v>128.3152084194042</v>
       </c>
     </row>
     <row r="131">
@@ -17480,31 +15147,13 @@
         <v>62.93763105608939</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>11.07786875200351</v>
+        <v>108.4061501827298</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>11.31025933517462</v>
+        <v>116.9261229859222</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>12.37436739955088</v>
-      </c>
-      <c r="K131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="4" t="n">
-        <v>5.705411133724917</v>
-      </c>
-      <c r="M131" s="4" t="n">
-        <v>12.51509539010627</v>
-      </c>
-      <c r="N131" s="4" t="n">
-        <v>137.5930028335124</v>
-      </c>
-      <c r="O131" s="4" t="n">
-        <v>159.3746544307396</v>
-      </c>
-      <c r="P131" s="4" t="n">
-        <v>187.9577092795602</v>
+        <v>127.413458453061</v>
       </c>
     </row>
     <row r="132">
@@ -17530,31 +15179,13 @@
         <v>62.93763105608939</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>11.12002569527996</v>
+        <v>107.9660477634717</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>11.36986088425015</v>
+        <v>116.4860205666641</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>12.31045009057822</v>
-      </c>
-      <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="4" t="n">
-        <v>5.721358959570146</v>
-      </c>
-      <c r="M132" s="4" t="n">
-        <v>12.55007771776677</v>
-      </c>
-      <c r="N132" s="4" t="n">
-        <v>137.2175858027863</v>
-      </c>
-      <c r="O132" s="4" t="n">
-        <v>159.0626350535539</v>
-      </c>
-      <c r="P132" s="4" t="n">
-        <v>187.1617359764814</v>
+        <v>126.9733560338029</v>
       </c>
     </row>
     <row r="133">
@@ -17580,31 +15211,13 @@
         <v>62.5697047204061</v>
       </c>
       <c r="H133" s="4" t="n">
-        <v>11.37201088280771</v>
+        <v>109.6377153505708</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>11.642914044436</v>
+        <v>118.0455705195615</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>12.79742177329385</v>
-      </c>
-      <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="4" t="n">
-        <v>5.912526405180151</v>
-      </c>
-      <c r="M133" s="4" t="n">
-        <v>12.96941275975001</v>
-      </c>
-      <c r="N133" s="4" t="n">
-        <v>139.1005532953906</v>
-      </c>
-      <c r="O133" s="4" t="n">
-        <v>161.159965594967</v>
-      </c>
-      <c r="P133" s="4" t="n">
-        <v>191.4035354589699</v>
+        <v>128.4048385902213</v>
       </c>
     </row>
     <row r="134">
@@ -17630,31 +15243,13 @@
         <v>61.76356561160463</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>11.403331385273</v>
+        <v>111.9237701186188</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>11.67423454690129</v>
+        <v>120.1652896608715</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>12.82874227575914</v>
-      </c>
-      <c r="K134" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="4" t="n">
-        <v>5.977604940806528</v>
-      </c>
-      <c r="M134" s="4" t="n">
-        <v>13.11216567660787</v>
-      </c>
-      <c r="N134" s="4" t="n">
-        <v>141.5846984385006</v>
-      </c>
-      <c r="O134" s="4" t="n">
-        <v>163.8233654860963</v>
-      </c>
-      <c r="P134" s="4" t="n">
-        <v>193.734180736655</v>
+        <v>130.3275189472404</v>
       </c>
     </row>
     <row r="135">
@@ -17680,31 +15275,13 @@
         <v>61.76356561160463</v>
       </c>
       <c r="H135" s="4" t="n">
-        <v>11.71396657986568</v>
+        <v>115.3144715331147</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11.96768518196372</v>
+        <v>123.5559910753674</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>13.06762839908964</v>
-      </c>
-      <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="4" t="n">
-        <v>5.977604940806528</v>
-      </c>
-      <c r="M135" s="4" t="n">
-        <v>13.11216567660787</v>
-      </c>
-      <c r="N135" s="4" t="n">
-        <v>145.4082905692579</v>
-      </c>
-      <c r="O135" s="4" t="n">
-        <v>168.1614512400604</v>
-      </c>
-      <c r="P135" s="4" t="n">
-        <v>198.668309550743</v>
+        <v>133.7182203617364</v>
       </c>
     </row>
     <row r="136">
@@ -17730,31 +15307,13 @@
         <v>61.76044258013457</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>11.91861629810981</v>
+        <v>118.5227039446897</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>12.21647862080549</v>
+        <v>126.7521139789989</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>13.16872040676451</v>
-      </c>
-      <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="4" t="n">
-        <v>6.322958373215415</v>
-      </c>
-      <c r="M136" s="4" t="n">
-        <v>13.86971514124672</v>
-      </c>
-      <c r="N136" s="4" t="n">
-        <v>148.9077594759167</v>
-      </c>
-      <c r="O136" s="4" t="n">
-        <v>172.0159730277105</v>
-      </c>
-      <c r="P136" s="4" t="n">
-        <v>202.9696594154133</v>
+        <v>136.9233297418413</v>
       </c>
     </row>
     <row r="137">
@@ -17780,31 +15339,13 @@
         <v>61.73260758372812</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>11.91861629810981</v>
+        <v>117.689400338839</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>12.21647862080549</v>
+        <v>126.0174016743031</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>13.16872040676451</v>
-      </c>
-      <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="4" t="n">
-        <v>6.34305733757692</v>
-      </c>
-      <c r="M137" s="4" t="n">
-        <v>13.91380319210421</v>
-      </c>
-      <c r="N137" s="4" t="n">
-        <v>147.9641030081546</v>
-      </c>
-      <c r="O137" s="4" t="n">
-        <v>170.5700805248368</v>
-      </c>
-      <c r="P137" s="4" t="n">
-        <v>201.0180632079094</v>
+        <v>136.2449099699511</v>
       </c>
     </row>
     <row r="138">
@@ -17830,31 +15371,13 @@
         <v>61.01725401789081</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>12.27848125585073</v>
+        <v>116.2188378439331</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>12.57634357854641</v>
+        <v>124.435789754665</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>13.52858536450544</v>
-      </c>
-      <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="4" t="n">
-        <v>6.791403220404523</v>
-      </c>
-      <c r="M138" s="4" t="n">
-        <v>14.89727158024218</v>
-      </c>
-      <c r="N138" s="4" t="n">
-        <v>146.3117067493657</v>
-      </c>
-      <c r="O138" s="4" t="n">
-        <v>169.395066271154</v>
-      </c>
-      <c r="P138" s="4" t="n">
-        <v>200.4804896670514</v>
+        <v>134.5539546417753</v>
       </c>
     </row>
     <row r="139">
@@ -17880,31 +15403,13 @@
         <v>57.35569380366108</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>12.25689851963186</v>
+        <v>113.1144487967722</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>12.54872189273756</v>
+        <v>120.8326863839892</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>13.62153489418784</v>
-      </c>
-      <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="4" t="n">
-        <v>7.119103771101006</v>
-      </c>
-      <c r="M139" s="4" t="n">
-        <v>15.61609859467317</v>
-      </c>
-      <c r="N139" s="4" t="n">
-        <v>142.2879375970092</v>
-      </c>
-      <c r="O139" s="4" t="n">
-        <v>164.5626534021316</v>
-      </c>
-      <c r="P139" s="4" t="n">
-        <v>194.8736923283773</v>
+        <v>130.3388031783896</v>
       </c>
     </row>
     <row r="140">
@@ -17930,31 +15435,13 @@
         <v>56.41400616416499</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>12.18671752825629</v>
+        <v>111.9695852855459</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>12.4658696527668</v>
+        <v>119.5332699081912</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>13.54716110323055</v>
-      </c>
-      <c r="K140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="4" t="n">
-        <v>7.119103771101006</v>
-      </c>
-      <c r="M140" s="4" t="n">
-        <v>15.61609859467317</v>
-      </c>
-      <c r="N140" s="4" t="n">
-        <v>140.9802196485721</v>
-      </c>
-      <c r="O140" s="4" t="n">
-        <v>163.1247900332236</v>
-      </c>
-      <c r="P140" s="4" t="n">
-        <v>193.8298122168182</v>
+        <v>128.8549825177683</v>
       </c>
     </row>
     <row r="141">
@@ -17980,31 +15467,13 @@
         <v>56.29869856104289</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>12.18671752825629</v>
+        <v>110.5883076262492</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>12.4658696527668</v>
+        <v>118.1519544938775</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>13.54716110323055</v>
-      </c>
-      <c r="K141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="4" t="n">
-        <v>7.119103771101006</v>
-      </c>
-      <c r="M141" s="4" t="n">
-        <v>15.61609859467317</v>
-      </c>
-      <c r="N141" s="4" t="n">
-        <v>139.4987316818485</v>
-      </c>
-      <c r="O141" s="4" t="n">
-        <v>161.5644866404496</v>
-      </c>
-      <c r="P141" s="4" t="n">
-        <v>192.7997552503135</v>
+        <v>127.4693261753508</v>
       </c>
     </row>
     <row r="142">
@@ -18030,31 +15499,13 @@
         <v>52.25861005255693</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>12.18671752825629</v>
+        <v>92.870122254032</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>12.4658696527668</v>
+        <v>99.80856496186232</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>13.54716110323055</v>
-      </c>
-      <c r="K142" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" s="4" t="n">
-        <v>7.256336448858398</v>
-      </c>
-      <c r="M142" s="4" t="n">
-        <v>15.91712511362487</v>
-      </c>
-      <c r="N142" s="4" t="n">
-        <v>120.7089363275807</v>
-      </c>
-      <c r="O142" s="4" t="n">
-        <v>142.6900851634272</v>
-      </c>
-      <c r="P142" s="4" t="n">
-        <v>173.0223063668312</v>
+        <v>108.3731310521763</v>
       </c>
     </row>
     <row r="143">
@@ -18080,31 +15531,13 @@
         <v>52.05714330347582</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>12.32044295101338</v>
+        <v>82.65217821160951</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>12.64733364785621</v>
+        <v>89.58534645712695</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>13.8710050861352</v>
-      </c>
-      <c r="K143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="4" t="n">
-        <v>7.256336448858398</v>
-      </c>
-      <c r="M143" s="4" t="n">
-        <v>15.91712511362487</v>
-      </c>
-      <c r="N143" s="4" t="n">
-        <v>110.4183833374845</v>
-      </c>
-      <c r="O143" s="4" t="n">
-        <v>132.3534971967578</v>
-      </c>
-      <c r="P143" s="4" t="n">
-        <v>163.7324458154162</v>
+        <v>98.14550796109746</v>
       </c>
     </row>
     <row r="144">
@@ -18130,31 +15563,13 @@
         <v>51.17003850492144</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>11.67599304367287</v>
+        <v>78.06173057096481</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>12.01390161384916</v>
+        <v>84.84199489999725</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>13.1241403700681</v>
-      </c>
-      <c r="K144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="4" t="n">
-        <v>7.256336448858398</v>
-      </c>
-      <c r="M144" s="4" t="n">
-        <v>15.91712511362487</v>
-      </c>
-      <c r="N144" s="4" t="n">
-        <v>104.9994941236386</v>
-      </c>
-      <c r="O144" s="4" t="n">
-        <v>126.4538578951033</v>
-      </c>
-      <c r="P144" s="4" t="n">
-        <v>156.4101867696901</v>
+        <v>93.21714250872492</v>
       </c>
     </row>
     <row r="145">
@@ -18180,31 +15595,13 @@
         <v>51.16775432025197</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>12.12522948126554</v>
+        <v>75.78334504813182</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>12.52421482479282</v>
+        <v>82.6092393032129</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>13.64313870201538</v>
-      </c>
-      <c r="K145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="4" t="n">
-        <v>7.256336448858398</v>
-      </c>
-      <c r="M145" s="4" t="n">
-        <v>15.91712511362487</v>
-      </c>
-      <c r="N145" s="4" t="n">
-        <v>103.0853343137239</v>
-      </c>
-      <c r="O145" s="4" t="n">
-        <v>124.1562493533361</v>
-      </c>
-      <c r="P145" s="4" t="n">
-        <v>154.2656194448019</v>
+        <v>91.03610687196939</v>
       </c>
     </row>
     <row r="146">
@@ -18230,31 +15627,13 @@
         <v>51.16775432025197</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>12.55510599794845</v>
+        <v>75.14112116688239</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>13.05420224610452</v>
+        <v>81.96701542196348</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>14.28721950798114</v>
-      </c>
-      <c r="K146" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="4" t="n">
-        <v>7.256336448858398</v>
-      </c>
-      <c r="M146" s="4" t="n">
-        <v>15.91712511362487</v>
-      </c>
-      <c r="N146" s="4" t="n">
-        <v>102.8637269459738</v>
-      </c>
-      <c r="O146" s="4" t="n">
-        <v>124.2817176944795</v>
-      </c>
-      <c r="P146" s="4" t="n">
-        <v>155.4615573591311</v>
+        <v>90.39388299071996</v>
       </c>
     </row>
     <row r="147">
@@ -18280,31 +15659,13 @@
         <v>51.16775432025197</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>12.45548377534882</v>
+        <v>60.77115019257625</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>12.87196246648515</v>
+        <v>67.59704444765734</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>14.16426733148408</v>
-      </c>
-      <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="n">
-        <v>7.57298201805271</v>
-      </c>
-      <c r="M147" s="4" t="n">
-        <v>16.6117024912124</v>
-      </c>
-      <c r="N147" s="4" t="n">
-        <v>88.58732554949826</v>
-      </c>
-      <c r="O147" s="4" t="n">
-        <v>110.2657091676311</v>
-      </c>
-      <c r="P147" s="4" t="n">
-        <v>142.6140265578986</v>
+        <v>76.02391201641383</v>
       </c>
     </row>
     <row r="148">
@@ -18330,31 +15691,13 @@
         <v>51.17003850492144</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>12.38329213424667</v>
+        <v>45.72563951116918</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>12.80479020587382</v>
+        <v>52.55153376625027</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>14.08492950005634</v>
-      </c>
-      <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="4" t="n">
-        <v>7.57298201805271</v>
-      </c>
-      <c r="M148" s="4" t="n">
-        <v>16.6117024912124</v>
-      </c>
-      <c r="N148" s="4" t="n">
-        <v>73.46910791615151</v>
-      </c>
-      <c r="O148" s="4" t="n">
-        <v>94.9170814513846</v>
-      </c>
-      <c r="P148" s="4" t="n">
-        <v>127.3650430215957</v>
+        <v>60.98068551967624</v>
       </c>
     </row>
     <row r="149">
@@ -18380,31 +15723,13 @@
         <v>51.04542304086161</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>12.16605905089994</v>
+        <v>43.01608381460156</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>12.65046293721618</v>
+        <v>49.82810759640721</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>13.91808841977694</v>
-      </c>
-      <c r="K149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="4" t="n">
-        <v>7.57298201805271</v>
-      </c>
-      <c r="M149" s="4" t="n">
-        <v>16.6117024912124</v>
-      </c>
-      <c r="N149" s="4" t="n">
-        <v>70.42027440781465</v>
-      </c>
-      <c r="O149" s="4" t="n">
-        <v>91.99015712435396</v>
-      </c>
-      <c r="P149" s="4" t="n">
-        <v>123.2127074304255</v>
+        <v>58.24022578502456</v>
       </c>
     </row>
     <row r="150">
@@ -18430,31 +15755,13 @@
         <v>51.04542304086161</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>11.71349598413167</v>
+        <v>41.80642801719944</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>12.09778896581912</v>
+        <v>48.61845179900508</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>13.25132106372582</v>
-      </c>
-      <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v>7.731611965448666</v>
-      </c>
-      <c r="M150" s="4" t="n">
-        <v>16.95966495646804</v>
-      </c>
-      <c r="N150" s="4" t="n">
-        <v>68.73979253260727</v>
-      </c>
-      <c r="O150" s="4" t="n">
-        <v>90.38645730295072</v>
-      </c>
-      <c r="P150" s="4" t="n">
-        <v>119.9637640928106</v>
+        <v>57.03056998762243</v>
       </c>
     </row>
     <row r="151">
@@ -18480,31 +15787,13 @@
         <v>51.04542304086161</v>
       </c>
       <c r="H151" s="4" t="n">
-        <v>11.14614977111126</v>
+        <v>41.68678809862875</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>11.47120257847227</v>
+        <v>48.49881188043439</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>12.76630184925695</v>
-      </c>
-      <c r="K151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="4" t="n">
-        <v>8.015242375542845</v>
-      </c>
-      <c r="M151" s="4" t="n">
-        <v>17.58182198506173</v>
-      </c>
-      <c r="N151" s="4" t="n">
-        <v>68.12740692640469</v>
-      </c>
-      <c r="O151" s="4" t="n">
-        <v>89.58707153892435</v>
-      </c>
-      <c r="P151" s="4" t="n">
-        <v>120.0245204648712</v>
+        <v>56.91093006905174</v>
       </c>
     </row>
     <row r="152">
@@ -18530,31 +15819,13 @@
         <v>48.71589273993403</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>10.89411925720225</v>
+        <v>39.40373774101162</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>11.18899197588225</v>
+        <v>45.90590050961428</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>12.3414122296849</v>
-      </c>
-      <c r="K152" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="4" t="n">
-        <v>8.268967116722878</v>
-      </c>
-      <c r="M152" s="4" t="n">
-        <v>18.13837948184373</v>
-      </c>
-      <c r="N152" s="4" t="n">
-        <v>64.65535151911592</v>
-      </c>
-      <c r="O152" s="4" t="n">
-        <v>86.43497586654227</v>
-      </c>
-      <c r="P152" s="4" t="n">
-        <v>117.2152948271722</v>
+        <v>53.93726381119891</v>
       </c>
     </row>
     <row r="153">
@@ -18580,31 +15851,13 @@
         <v>47.74378809067358</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>11.82206507924842</v>
+        <v>38.44706518195516</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>12.2835525490035</v>
+        <v>44.83173361516326</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>13.40874177967873</v>
-      </c>
-      <c r="K153" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="4" t="n">
-        <v>8.268967116722878</v>
-      </c>
-      <c r="M153" s="4" t="n">
-        <v>18.13837948184373</v>
-      </c>
-      <c r="N153" s="4" t="n">
-        <v>64.31793770266135</v>
-      </c>
-      <c r="O153" s="4" t="n">
-        <v>86.08282513854938</v>
-      </c>
-      <c r="P153" s="4" t="n">
-        <v>117.3008389057054</v>
+        <v>52.71346259226419</v>
       </c>
     </row>
     <row r="154">
@@ -18630,31 +15883,13 @@
         <v>46.2180647960069</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>12.38494848223782</v>
+        <v>36.83620763871947</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>12.88349012433302</v>
+        <v>43.0320042515458</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>14.11587026069728</v>
-      </c>
-      <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="n">
-        <v>8.268967116722878</v>
-      </c>
-      <c r="M154" s="4" t="n">
-        <v>18.13837948184373</v>
-      </c>
-      <c r="N154" s="4" t="n">
-        <v>63.2247785027129</v>
-      </c>
-      <c r="O154" s="4" t="n">
-        <v>85.36021341602941</v>
-      </c>
-      <c r="P154" s="4" t="n">
-        <v>118.8344493165579</v>
+        <v>50.67796470609768</v>
       </c>
     </row>
     <row r="155">
@@ -18680,31 +15915,13 @@
         <v>45.97504392741821</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>11.7886727798223</v>
+        <v>35.39990130310576</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>12.18559870993289</v>
+        <v>41.54830991489443</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>13.40789068104366</v>
-      </c>
-      <c r="K155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="4" t="n">
-        <v>8.268967116722878</v>
-      </c>
-      <c r="M155" s="4" t="n">
-        <v>18.13837948184373</v>
-      </c>
-      <c r="N155" s="4" t="n">
-        <v>61.26730234136809</v>
-      </c>
-      <c r="O155" s="4" t="n">
-        <v>82.31167808096748</v>
-      </c>
-      <c r="P155" s="4" t="n">
-        <v>112.8410791382712</v>
+        <v>49.13444620284304</v>
       </c>
     </row>
     <row r="156">
@@ -18730,31 +15947,13 @@
         <v>45.86769835494262</v>
       </c>
       <c r="H156" s="4" t="n">
-        <v>10.70189796019469</v>
+        <v>35.02218652881396</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>10.97827596466677</v>
+        <v>41.15521082052882</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>12.05402296297958</v>
-      </c>
-      <c r="K156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" s="4" t="n">
-        <v>8.268967116722878</v>
-      </c>
-      <c r="M156" s="4" t="n">
-        <v>18.13837948184373</v>
-      </c>
-      <c r="N156" s="4" t="n">
-        <v>59.72215748116989</v>
-      </c>
-      <c r="O156" s="4" t="n">
-        <v>80.03927778073063</v>
-      </c>
-      <c r="P156" s="4" t="n">
-        <v>108.9955706705386</v>
+        <v>48.72544287027903</v>
       </c>
     </row>
     <row r="157">
@@ -18780,31 +15979,13 @@
         <v>45.04418124402025</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>11.11476404227633</v>
+        <v>34.44696385395</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>11.40689577449218</v>
+        <v>40.46652370713046</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>12.46993693288314</v>
-      </c>
-      <c r="K157" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" s="4" t="n">
-        <v>7.731611965448666</v>
-      </c>
-      <c r="M157" s="4" t="n">
-        <v>16.95966495646804</v>
-      </c>
-      <c r="N157" s="4" t="n">
-        <v>59.35962010874169</v>
-      </c>
-      <c r="O157" s="4" t="n">
-        <v>78.56877121986254</v>
-      </c>
-      <c r="P157" s="4" t="n">
-        <v>106.0170766092607</v>
+        <v>47.896365271197</v>
       </c>
     </row>
     <row r="158">
@@ -18830,31 +16011,13 @@
         <v>36.34733748479648</v>
       </c>
       <c r="H158" s="4" t="n">
-        <v>11.29963276749799</v>
+        <v>28.29427476749504</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>11.58344326573854</v>
+        <v>33.13905949243653</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>12.67146632461702</v>
-      </c>
-      <c r="K158" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" s="4" t="n">
-        <v>7.356400297647311</v>
-      </c>
-      <c r="M158" s="4" t="n">
-        <v>16.13662000774249</v>
-      </c>
-      <c r="N158" s="4" t="n">
-        <v>51.08261026520253</v>
-      </c>
-      <c r="O158" s="4" t="n">
-        <v>67.92208664559307</v>
-      </c>
-      <c r="P158" s="4" t="n">
-        <v>92.29225710344768</v>
+        <v>39.11639752078261</v>
       </c>
     </row>
     <row r="159">
@@ -18880,31 +16043,13 @@
         <v>36.29643670998625</v>
       </c>
       <c r="H159" s="4" t="n">
-        <v>11.34402696685531</v>
+        <v>28.23008092554552</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>11.58763004111845</v>
+        <v>33.066925847093</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>12.62701524679965</v>
-      </c>
-      <c r="K159" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="4" t="n">
-        <v>7.087345718492998</v>
-      </c>
-      <c r="M159" s="4" t="n">
-        <v>15.54643576959754</v>
-      </c>
-      <c r="N159" s="4" t="n">
-        <v>51.00304373623568</v>
-      </c>
-      <c r="O159" s="4" t="n">
-        <v>67.50545921928017</v>
-      </c>
-      <c r="P159" s="4" t="n">
-        <v>91.69291117422542</v>
+        <v>39.03413064772299</v>
       </c>
     </row>
     <row r="160">
@@ -18930,31 +16075,13 @@
         <v>36.26675027154675</v>
       </c>
       <c r="H160" s="4" t="n">
-        <v>11.34402696685531</v>
+        <v>28.0129348413021</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>11.58763004111845</v>
+        <v>32.84310750172938</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>12.62238944855059</v>
-      </c>
-      <c r="K160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="4" t="n">
-        <v>7.076616989351081</v>
-      </c>
-      <c r="M160" s="4" t="n">
-        <v>15.52290178309269</v>
-      </c>
-      <c r="N160" s="4" t="n">
-        <v>50.77703622317864</v>
-      </c>
-      <c r="O160" s="4" t="n">
-        <v>67.26044295963446</v>
-      </c>
-      <c r="P160" s="4" t="n">
-        <v>91.580420460087</v>
+        <v>38.80292945666127</v>
       </c>
     </row>
     <row r="161">
@@ -18980,31 +16107,13 @@
         <v>36.20489051987443</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>11.33761345025583</v>
+        <v>27.92982348485562</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>11.58146397022706</v>
+        <v>32.75492792885728</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>12.60237469913745</v>
-      </c>
-      <c r="K161" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" s="4" t="n">
-        <v>7.076616989351081</v>
-      </c>
-      <c r="M161" s="4" t="n">
-        <v>15.52290178309269</v>
-      </c>
-      <c r="N161" s="4" t="n">
-        <v>50.60945566421865</v>
-      </c>
-      <c r="O161" s="4" t="n">
-        <v>67.34473267803801</v>
-      </c>
-      <c r="P161" s="4" t="n">
-        <v>91.64426145426836</v>
+        <v>38.70831433007938</v>
       </c>
     </row>
     <row r="162">
@@ -19030,31 +16139,13 @@
         <v>33.87859811434832</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>11.21148902804552</v>
+        <v>26.29210199179988</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>11.44395221324467</v>
+        <v>30.79418498701409</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>12.489415215713</v>
-      </c>
-      <c r="K162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="4" t="n">
-        <v>7.076616989351081</v>
-      </c>
-      <c r="M162" s="4" t="n">
-        <v>15.52290178309269</v>
-      </c>
-      <c r="N162" s="4" t="n">
-        <v>48.34483918556545</v>
-      </c>
-      <c r="O162" s="4" t="n">
-        <v>64.4769364165296</v>
-      </c>
-      <c r="P162" s="4" t="n">
-        <v>88.32219759687813</v>
+        <v>36.37544604493461</v>
       </c>
     </row>
     <row r="163">
@@ -19080,31 +16171,13 @@
         <v>34.74134248946862</v>
       </c>
       <c r="H163" s="4" t="n">
-        <v>10.97767072319412</v>
+        <v>26.73288540196064</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>11.18215073058952</v>
+        <v>31.41677983758479</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>12.16640009744129</v>
-      </c>
-      <c r="K163" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" s="4" t="n">
-        <v>7.087345718492998</v>
-      </c>
-      <c r="M163" s="4" t="n">
-        <v>15.54643576959754</v>
-      </c>
-      <c r="N163" s="4" t="n">
-        <v>48.57316917910902</v>
-      </c>
-      <c r="O163" s="4" t="n">
-        <v>64.54312153361458</v>
-      </c>
-      <c r="P163" s="4" t="n">
-        <v>88.49646130820028</v>
+        <v>37.21679680725287</v>
       </c>
     </row>
     <row r="164">
@@ -19130,31 +16203,13 @@
         <v>35.58501537214921</v>
       </c>
       <c r="H164" s="4" t="n">
-        <v>10.88029336189477</v>
+        <v>27.32806916903179</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>11.06923882849976</v>
+        <v>32.09672094656644</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>12.07342562698976</v>
-      </c>
-      <c r="K164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="4" t="n">
-        <v>7.131012290503135</v>
-      </c>
-      <c r="M164" s="4" t="n">
-        <v>15.64222050820043</v>
-      </c>
-      <c r="N164" s="4" t="n">
-        <v>49.27921585724444</v>
-      </c>
-      <c r="O164" s="4" t="n">
-        <v>65.20214244060882</v>
-      </c>
-      <c r="P164" s="4" t="n">
-        <v>88.86817135849</v>
+        <v>37.99189056888041</v>
       </c>
     </row>
     <row r="165">
@@ -19180,31 +16235,13 @@
         <v>35.5018941561318</v>
       </c>
       <c r="H165" s="4" t="n">
-        <v>10.68716581545337</v>
+        <v>27.36051250648621</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>10.86748197046189</v>
+        <v>32.07083484360085</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>11.80145024323786</v>
-      </c>
-      <c r="K165" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" s="4" t="n">
-        <v>7.356400297647311</v>
-      </c>
-      <c r="M165" s="4" t="n">
-        <v>16.13662000774249</v>
-      </c>
-      <c r="N165" s="4" t="n">
-        <v>49.08022257935477</v>
-      </c>
-      <c r="O165" s="4" t="n">
-        <v>65.14085754217471</v>
-      </c>
-      <c r="P165" s="4" t="n">
-        <v>88.27861462319673</v>
+        <v>37.90672214011433</v>
       </c>
     </row>
     <row r="166">
@@ -19230,31 +16267,13 @@
         <v>36.6757234370206</v>
       </c>
       <c r="H166" s="4" t="n">
-        <v>10.44181586131967</v>
+        <v>28.05825920899447</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>10.61314603589485</v>
+        <v>32.95807063116518</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>11.54036016949352</v>
-      </c>
-      <c r="K166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="4" t="n">
-        <v>7.527439055314001</v>
-      </c>
-      <c r="M166" s="4" t="n">
-        <v>16.51180179875329</v>
-      </c>
-      <c r="N166" s="4" t="n">
-        <v>49.53261932772936</v>
-      </c>
-      <c r="O166" s="4" t="n">
-        <v>65.94456808028902</v>
-      </c>
-      <c r="P166" s="4" t="n">
-        <v>89.48513110661554</v>
+        <v>39.05636360131724</v>
       </c>
     </row>
     <row r="167">
@@ -19280,31 +16299,13 @@
         <v>36.6757234370206</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>10.31582736785856</v>
+        <v>27.98550448883394</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>10.47720152193086</v>
+        <v>32.88531591100464</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>11.39941011974365</v>
-      </c>
-      <c r="K167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="4" t="n">
-        <v>8.135919728641836</v>
-      </c>
-      <c r="M167" s="4" t="n">
-        <v>17.84653359831113</v>
-      </c>
-      <c r="N167" s="4" t="n">
-        <v>49.3338761141077</v>
-      </c>
-      <c r="O167" s="4" t="n">
-        <v>66.34434951949234</v>
-      </c>
-      <c r="P167" s="4" t="n">
-        <v>90.60615813626298</v>
+        <v>38.98360888115671</v>
       </c>
     </row>
     <row r="168">
@@ -19330,31 +16331,13 @@
         <v>36.6757234370206</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>10.26004641291209</v>
+        <v>27.79973388633449</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>10.42013568491995</v>
+        <v>32.6995453085052</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>11.33946876435463</v>
-      </c>
-      <c r="K168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="4" t="n">
-        <v>9.218514066473441</v>
-      </c>
-      <c r="M168" s="4" t="n">
-        <v>20.22125666194174</v>
-      </c>
-      <c r="N168" s="4" t="n">
-        <v>49.07695475564025</v>
-      </c>
-      <c r="O168" s="4" t="n">
-        <v>67.15104926964963</v>
-      </c>
-      <c r="P168" s="4" t="n">
-        <v>92.58120142504509</v>
+        <v>38.79783827865727</v>
       </c>
     </row>
     <row r="169">
@@ -19380,31 +16363,13 @@
         <v>36.71272531042836</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>10.08894560067384</v>
+        <v>27.7420724167582</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>10.2132235853379</v>
+        <v>32.65052562442815</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>11.08974705620863</v>
-      </c>
-      <c r="K169" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" s="4" t="n">
-        <v>9.440326022316061</v>
-      </c>
-      <c r="M169" s="4" t="n">
-        <v>20.7078119199191</v>
-      </c>
-      <c r="N169" s="4" t="n">
-        <v>48.88969857389999</v>
-      </c>
-      <c r="O169" s="4" t="n">
-        <v>67.14190276439378</v>
-      </c>
-      <c r="P169" s="4" t="n">
-        <v>92.07174805724618</v>
+        <v>38.75808622352609</v>
       </c>
     </row>
     <row r="170">
@@ -19430,31 +16395,13 @@
         <v>36.88668276972912</v>
       </c>
       <c r="H170" s="4" t="n">
-        <v>9.969233696447381</v>
+        <v>27.71636730792595</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>10.07936418598451</v>
+        <v>32.64861899202401</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>10.92416741175233</v>
-      </c>
-      <c r="K170" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" s="4" t="n">
-        <v>9.75536736294775</v>
-      </c>
-      <c r="M170" s="4" t="n">
-        <v>21.39887034453055</v>
-      </c>
-      <c r="N170" s="4" t="n">
-        <v>48.74693900835928</v>
-      </c>
-      <c r="O170" s="4" t="n">
-        <v>67.35613789956295</v>
-      </c>
-      <c r="P170" s="4" t="n">
-        <v>92.5311012289387</v>
+        <v>38.78675791218716</v>
       </c>
     </row>
     <row r="171">
@@ -19480,31 +16427,13 @@
         <v>39.10062088911857</v>
       </c>
       <c r="H171" s="4" t="n">
-        <v>9.834777788623684</v>
+        <v>29.12845417285389</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>9.936823522290569</v>
+        <v>34.35021016799062</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>10.76905892768995</v>
-      </c>
-      <c r="K171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="4" t="n">
-        <v>11.03856493694976</v>
-      </c>
-      <c r="M171" s="4" t="n">
-        <v>24.21362631330916</v>
-      </c>
-      <c r="N171" s="4" t="n">
-        <v>50.91389564728052</v>
-      </c>
-      <c r="O171" s="4" t="n">
-        <v>71.24201299725395</v>
-      </c>
-      <c r="P171" s="4" t="n">
-        <v>98.52218333936554</v>
+        <v>40.84489038761549</v>
       </c>
     </row>
     <row r="172">
@@ -19530,31 +16459,13 @@
         <v>37.43680446390308</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>9.34417649453899</v>
+        <v>27.89886832396027</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>9.397685543979277</v>
+        <v>32.82883907093748</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>9.953707930689944</v>
-      </c>
-      <c r="K172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="4" t="n">
-        <v>11.03856493694976</v>
-      </c>
-      <c r="M172" s="4" t="n">
-        <v>24.21362631330916</v>
-      </c>
-      <c r="N172" s="4" t="n">
-        <v>49.19949507453377</v>
-      </c>
-      <c r="O172" s="4" t="n">
-        <v>68.8940860853444</v>
-      </c>
-      <c r="P172" s="4" t="n">
-        <v>94.07139420498922</v>
+        <v>38.95893063821953</v>
       </c>
     </row>
     <row r="173">
@@ -19580,41 +16491,21 @@
         <v>37.43680446390308</v>
       </c>
       <c r="H173" s="4" t="n">
-        <v>9.338389924307426</v>
+        <v>27.89886832396027</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>9.390371223962417</v>
+        <v>32.82883907093748</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>9.938745862343144</v>
-      </c>
-      <c r="K173" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="4" t="n">
-        <v>11.03856493694976</v>
-      </c>
-      <c r="M173" s="4" t="n">
-        <v>24.21362631330916</v>
-      </c>
-      <c r="N173" s="4" t="n">
-        <v>49.19949507453377</v>
-      </c>
-      <c r="O173" s="4" t="n">
-        <v>68.8940860853444</v>
-      </c>
-      <c r="P173" s="4" t="n">
-        <v>94.07139420498922</v>
+        <v>38.95893063821953</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23660,7 +20551,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-08 20:33 by Paper/make_supplementary_datasets.py. Rerun that script after any change to the workflow so these numbers stay in step with the analysis.</t>
+          <t>Generated 2026-09-16 07:05 by Paper/make_supplementary_datasets.py. Rerun that script after any change to the workflow so these numbers stay in step with the analysis.</t>
         </is>
       </c>
     </row>

--- a/supplementary/Supplementary_Dataset_S2_carbon_model.xlsx
+++ b/supplementary/Supplementary_Dataset_S2_carbon_model.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -585,67 +585,74 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    their sum. Serpentinite carbon is mantle-derived and returns to the mantle rather than</t>
+          <t xml:space="preserve">    their sum. Serpentinite and mantle lithosphere carbon are mantle-derived and return to the</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    representing a sink of surface carbon, so it is excluded, as is organic carbon; neither</t>
+          <t xml:space="preserve">    mantle rather than representing a sink of surface carbon, so both are excluded, as is</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    enters the attribution behind Figure 4.</t>
+          <t xml:space="preserve">    organic carbon. None of the three enters the attribution behind Figure 4, whose</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    biological sink is pelagic sediment plus altered oceanic crust.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Sources (files in the CCD_workflow_clean repository, steps/step10_carbon_cycle_degassing/</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Alfonso_etal_2024_DM26/Outputs):</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Atmospheric outflux: Notebook05/csv/05_atmospheric_influx_all_sources.csv</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Plate influx: Notebook02/csv/02_plate_influx.csv</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Net flux: Notebook05/csv/05_net_carbon_outflux.csv</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>See the Provenance sheet for the exact files used and when they were last written.</t>
         </is>
@@ -20551,7 +20558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-16 07:05 by Paper/make_supplementary_datasets.py. Rerun that script after any change to the workflow so these numbers stay in step with the analysis.</t>
+          <t>Generated 2026-09-16 07:07 by Paper/make_supplementary_datasets.py. Rerun that script after any change to the workflow so these numbers stay in step with the analysis.</t>
         </is>
       </c>
     </row>
